--- a/ZonasEscolares/excels/PUNO-SAN_ROMAN-JULIACA.xlsx
+++ b/ZonasEscolares/excels/PUNO-SAN_ROMAN-JULIACA.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>mantenimiento</t>
+          <t>Intervenido PI2024</t>
         </is>
       </c>
     </row>
@@ -503,7 +503,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -555,7 +555,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -607,7 +607,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -659,7 +659,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -815,7 +815,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -971,7 +971,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1179,7 +1179,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1231,7 +1231,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1439,7 +1439,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1491,7 +1491,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1543,7 +1543,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1595,7 +1595,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1751,7 +1751,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1907,7 +1907,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1959,7 +1959,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1994,7 +1994,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2098,7 +2098,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2115,7 +2115,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2167,7 +2167,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2219,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2323,7 +2323,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2375,7 +2375,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2427,7 +2427,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2462,7 +2462,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2479,7 +2479,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2531,7 +2531,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2583,7 +2583,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2635,7 +2635,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2687,7 +2687,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2722,7 +2722,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2843,7 +2843,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2895,7 +2895,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2947,7 +2947,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2982,7 +2982,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2999,7 +2999,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3034,7 +3034,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3155,7 +3155,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3190,7 +3190,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3207,7 +3207,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3259,7 +3259,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3311,7 +3311,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3346,7 +3346,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3363,7 +3363,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3415,7 +3415,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3467,7 +3467,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3502,7 +3502,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3519,7 +3519,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3554,7 +3554,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3571,7 +3571,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3623,7 +3623,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3658,7 +3658,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3727,7 +3727,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3762,7 +3762,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3779,7 +3779,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3814,7 +3814,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3831,7 +3831,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3883,7 +3883,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3918,7 +3918,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3935,7 +3935,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -3970,7 +3970,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4039,7 +4039,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4091,7 +4091,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4143,7 +4143,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4195,7 +4195,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4247,7 +4247,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -4282,7 +4282,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -4334,7 +4334,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4351,7 +4351,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4403,7 +4403,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -4438,7 +4438,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4455,7 +4455,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -4490,7 +4490,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4507,7 +4507,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -4542,7 +4542,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4559,7 +4559,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4611,7 +4611,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4663,7 +4663,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4698,7 +4698,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4715,7 +4715,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -4750,7 +4750,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4767,7 +4767,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4819,7 +4819,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4854,7 +4854,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4871,7 +4871,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -4958,7 +4958,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4975,7 +4975,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -5010,7 +5010,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5027,7 +5027,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -5062,7 +5062,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5079,7 +5079,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5131,7 +5131,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -5166,7 +5166,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5183,7 +5183,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -5218,7 +5218,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5235,7 +5235,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -5270,7 +5270,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5287,7 +5287,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -5322,7 +5322,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5339,7 +5339,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -5374,7 +5374,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5391,7 +5391,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -5426,7 +5426,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5443,7 +5443,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -5478,7 +5478,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5495,7 +5495,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -5530,7 +5530,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5547,7 +5547,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5651,7 +5651,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -5686,7 +5686,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5703,7 +5703,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -5738,7 +5738,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5755,7 +5755,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/PUNO-SAN_ROMAN-JULIACA.xlsx
+++ b/ZonasEscolares/excels/PUNO-SAN_ROMAN-JULIACA.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,62 +417,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Intervenido PI2024</t>
         </is>
@@ -521,20 +509,30 @@
           <t>305</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-15.49314</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-70.13194</v>
-      </c>
-      <c r="I2" t="n">
-        <v>459</v>
-      </c>
-      <c r="J2" t="n">
-        <v>18</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-15.49314</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-70.13194</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>459</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,20 +571,30 @@
           <t>306 BARCIA BONIFFATI</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-15.4889</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-70.13864</v>
-      </c>
-      <c r="I3" t="n">
-        <v>261</v>
-      </c>
-      <c r="J3" t="n">
-        <v>11</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-15.4889</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-70.13864</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -625,20 +633,30 @@
           <t>308 NIÑO JESUS DE PRAGA</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-15.5023</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-70.1267</v>
-      </c>
-      <c r="I4" t="n">
-        <v>245</v>
-      </c>
-      <c r="J4" t="n">
-        <v>12</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-15.5023</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-70.1267</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>245</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -677,20 +695,30 @@
           <t>314</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-15.48499</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-70.14094</v>
-      </c>
-      <c r="I5" t="n">
-        <v>396</v>
-      </c>
-      <c r="J5" t="n">
-        <v>18</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-15.48499</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-70.14094</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>396</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -729,20 +757,30 @@
           <t>70536</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-15.487922</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-70.146288</v>
-      </c>
-      <c r="I6" t="n">
-        <v>840</v>
-      </c>
-      <c r="J6" t="n">
-        <v>36</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-15.487922</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-70.146288</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>840</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -781,20 +819,30 @@
           <t>70541 VIRGEN DE FATIMA</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-15.4931</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-70.13178000000001</v>
-      </c>
-      <c r="I7" t="n">
-        <v>830</v>
-      </c>
-      <c r="J7" t="n">
-        <v>32</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-15.4931</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-70.13178</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>830</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -833,20 +881,30 @@
           <t>70542</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-15.489797</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-70.138508</v>
-      </c>
-      <c r="I8" t="n">
-        <v>741</v>
-      </c>
-      <c r="J8" t="n">
-        <v>30</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-15.489797</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-70.138508</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>741</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -885,20 +943,30 @@
           <t>70545 TUPAC AMARU</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-15.48968</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-70.127713</v>
-      </c>
-      <c r="I9" t="n">
-        <v>764</v>
-      </c>
-      <c r="J9" t="n">
-        <v>33</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-15.48968</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-70.127713</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>764</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -937,20 +1005,30 @@
           <t>70546 SEÑOR DE HUANCA</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-15.50498</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-70.12675</v>
-      </c>
-      <c r="I10" t="n">
-        <v>710</v>
-      </c>
-      <c r="J10" t="n">
-        <v>29</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-15.50498</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-70.12675</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>710</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -989,20 +1067,30 @@
           <t>70547</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-15.484065</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-70.128818</v>
-      </c>
-      <c r="I11" t="n">
-        <v>865</v>
-      </c>
-      <c r="J11" t="n">
-        <v>38</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-15.484065</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-70.128818</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>865</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1041,20 +1129,30 @@
           <t>70548</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-15.49226</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-70.14352</v>
-      </c>
-      <c r="I12" t="n">
-        <v>651</v>
-      </c>
-      <c r="J12" t="n">
-        <v>30</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-15.49226</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-70.14352</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>651</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1093,20 +1191,30 @@
           <t>70549 VIRGEN DEL CARMEN</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-15.48992</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-70.15561</v>
-      </c>
-      <c r="I13" t="n">
-        <v>523</v>
-      </c>
-      <c r="J13" t="n">
-        <v>25</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-15.48992</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-70.15561</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>523</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1145,20 +1253,30 @@
           <t>70550 LOS LIBERTADORES</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-15.486474</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-70.12143500000001</v>
-      </c>
-      <c r="I14" t="n">
-        <v>1312</v>
-      </c>
-      <c r="J14" t="n">
-        <v>52</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-15.486474</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-70.121435</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1312</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1197,20 +1315,30 @@
           <t>70558</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>-15.49349</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-70.12271</v>
-      </c>
-      <c r="I15" t="n">
-        <v>487</v>
-      </c>
-      <c r="J15" t="n">
-        <v>23</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-15.49349</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-70.12271</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>487</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1249,20 +1377,30 @@
           <t>70560 SEÑOR DE LOS MILAGROS</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>-15.49694</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-70.1267</v>
-      </c>
-      <c r="I16" t="n">
-        <v>239</v>
-      </c>
-      <c r="J16" t="n">
-        <v>12</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-15.49694</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-70.1267</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>239</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1301,20 +1439,30 @@
           <t>70561</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>-15.49782</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-70.12072000000001</v>
-      </c>
-      <c r="I17" t="n">
-        <v>524</v>
-      </c>
-      <c r="J17" t="n">
-        <v>21</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-15.49782</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-70.12072</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>524</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1353,20 +1501,30 @@
           <t>70563 NUESTRA SEÑORA DEL CARMEN</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>-15.49952</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-70.14198</v>
-      </c>
-      <c r="I18" t="n">
-        <v>422</v>
-      </c>
-      <c r="J18" t="n">
-        <v>22</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-15.49952</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-70.14198</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>422</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1405,20 +1563,30 @@
           <t>70564</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>-15.48484</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-70.13979999999999</v>
-      </c>
-      <c r="I19" t="n">
-        <v>1002</v>
-      </c>
-      <c r="J19" t="n">
-        <v>41</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-15.48484</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-70.1398</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1002</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1457,20 +1625,30 @@
           <t>70565 MARIANO NUÑEZ</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>-15.49028</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-70.13373</v>
-      </c>
-      <c r="I20" t="n">
-        <v>914</v>
-      </c>
-      <c r="J20" t="n">
-        <v>37</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-15.49028</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-70.13373</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>914</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1509,20 +1687,30 @@
           <t>70576 MARISCAL JOSE DE SUCRE</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>-15.48838</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-70.13057000000001</v>
-      </c>
-      <c r="I21" t="n">
-        <v>521</v>
-      </c>
-      <c r="J21" t="n">
-        <v>25</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-15.48838</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-70.13057</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>521</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1561,20 +1749,30 @@
           <t>70607 JOSE BERNARDO ALCEDO RELUERTO</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>-15.47822</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-70.10937</v>
-      </c>
-      <c r="I22" t="n">
-        <v>543</v>
-      </c>
-      <c r="J22" t="n">
-        <v>26</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-15.47822</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-70.10937</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>543</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1613,20 +1811,30 @@
           <t>70610</t>
         </is>
       </c>
-      <c r="G23" t="n">
-        <v>-15.48097</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-70.15192999999999</v>
-      </c>
-      <c r="I23" t="n">
-        <v>634</v>
-      </c>
-      <c r="J23" t="n">
-        <v>28</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-15.48097</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-70.15193</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>634</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1665,20 +1873,30 @@
           <t>70612</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>-15.49005</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-70.11624</v>
-      </c>
-      <c r="I24" t="n">
-        <v>294</v>
-      </c>
-      <c r="J24" t="n">
-        <v>15</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-15.49005</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-70.11624</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>294</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1717,20 +1935,30 @@
           <t>70615</t>
         </is>
       </c>
-      <c r="G25" t="n">
-        <v>-15.47948</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-70.14709000000001</v>
-      </c>
-      <c r="I25" t="n">
-        <v>398</v>
-      </c>
-      <c r="J25" t="n">
-        <v>21</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-15.47948</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-70.14709</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>398</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -1769,20 +1997,30 @@
           <t>70617 CESAR VALLEJO</t>
         </is>
       </c>
-      <c r="G26" t="n">
-        <v>-15.47465</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-70.11238</v>
-      </c>
-      <c r="I26" t="n">
-        <v>680</v>
-      </c>
-      <c r="J26" t="n">
-        <v>28</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-15.47465</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>-70.11238</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>680</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -1821,20 +2059,30 @@
           <t>70619</t>
         </is>
       </c>
-      <c r="G27" t="n">
-        <v>-15.48494</v>
-      </c>
-      <c r="H27" t="n">
-        <v>-70.11835000000001</v>
-      </c>
-      <c r="I27" t="n">
-        <v>493</v>
-      </c>
-      <c r="J27" t="n">
-        <v>21</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-15.48494</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>-70.11835</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>493</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -1873,20 +2121,30 @@
           <t>70620</t>
         </is>
       </c>
-      <c r="G28" t="n">
-        <v>-15.47849</v>
-      </c>
-      <c r="H28" t="n">
-        <v>-70.13844</v>
-      </c>
-      <c r="I28" t="n">
-        <v>708</v>
-      </c>
-      <c r="J28" t="n">
-        <v>30</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-15.47849</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>-70.13844</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>708</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -1925,20 +2183,30 @@
           <t>70663 CARLOS DANTE NAVA SILVA</t>
         </is>
       </c>
-      <c r="G29" t="n">
-        <v>-15.479091</v>
-      </c>
-      <c r="H29" t="n">
-        <v>-70.115599</v>
-      </c>
-      <c r="I29" t="n">
-        <v>514</v>
-      </c>
-      <c r="J29" t="n">
-        <v>21</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-15.479091</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>-70.115599</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>514</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -1977,20 +2245,30 @@
           <t>71014 MANUEL NUÑEZ BUTRON</t>
         </is>
       </c>
-      <c r="G30" t="n">
-        <v>-15.499647</v>
-      </c>
-      <c r="H30" t="n">
-        <v>-70.131946</v>
-      </c>
-      <c r="I30" t="n">
-        <v>1384</v>
-      </c>
-      <c r="J30" t="n">
-        <v>62</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-15.499647</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>-70.131946</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1384</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -2029,20 +2307,30 @@
           <t>71015 SAN JUAN BOSCO</t>
         </is>
       </c>
-      <c r="G31" t="n">
-        <v>-15.49137</v>
-      </c>
-      <c r="H31" t="n">
-        <v>-70.13106000000001</v>
-      </c>
-      <c r="I31" t="n">
-        <v>1174</v>
-      </c>
-      <c r="J31" t="n">
-        <v>46</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-15.49137</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>-70.13106</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1174</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -2081,20 +2369,30 @@
           <t>71016 MARIA AUXILIADORA</t>
         </is>
       </c>
-      <c r="G32" t="n">
-        <v>-15.49429</v>
-      </c>
-      <c r="H32" t="n">
-        <v>-70.13477</v>
-      </c>
-      <c r="I32" t="n">
-        <v>1522</v>
-      </c>
-      <c r="J32" t="n">
-        <v>58</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-15.49429</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>-70.13477</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1522</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -2133,20 +2431,30 @@
           <t>LAS MERCEDES</t>
         </is>
       </c>
-      <c r="G33" t="n">
-        <v>-15.490577</v>
-      </c>
-      <c r="H33" t="n">
-        <v>-70.13901199999999</v>
-      </c>
-      <c r="I33" t="n">
-        <v>1990</v>
-      </c>
-      <c r="J33" t="n">
-        <v>84</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>-15.490577</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>-70.139012</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1990</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -2185,20 +2493,30 @@
           <t>JOSE ANTONIO ENCINAS</t>
         </is>
       </c>
-      <c r="G34" t="n">
-        <v>-15.487692</v>
-      </c>
-      <c r="H34" t="n">
-        <v>-70.12421500000001</v>
-      </c>
-      <c r="I34" t="n">
-        <v>2807</v>
-      </c>
-      <c r="J34" t="n">
-        <v>131</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>-15.487692</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>-70.124215</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2807</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -2237,20 +2555,30 @@
           <t>POLITECNICO REGIONAL LOS ANDES</t>
         </is>
       </c>
-      <c r="G35" t="n">
-        <v>-15.488678</v>
-      </c>
-      <c r="H35" t="n">
-        <v>-70.143998</v>
-      </c>
-      <c r="I35" t="n">
-        <v>2127</v>
-      </c>
-      <c r="J35" t="n">
-        <v>85</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>-15.488678</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>-70.143998</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2127</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -2289,20 +2617,30 @@
           <t>32 MARIANO H. CORNEJO</t>
         </is>
       </c>
-      <c r="G36" t="n">
-        <v>-15.50433</v>
-      </c>
-      <c r="H36" t="n">
-        <v>-70.12706</v>
-      </c>
-      <c r="I36" t="n">
-        <v>1952</v>
-      </c>
-      <c r="J36" t="n">
-        <v>99</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>-15.50433</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>-70.12706</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1952</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -2341,20 +2679,30 @@
           <t>JOSE MARIA ARGUEDAS</t>
         </is>
       </c>
-      <c r="G37" t="n">
-        <v>-15.50469</v>
-      </c>
-      <c r="H37" t="n">
-        <v>-70.13548</v>
-      </c>
-      <c r="I37" t="n">
-        <v>638</v>
-      </c>
-      <c r="J37" t="n">
-        <v>43</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0</v>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>-15.50469</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>-70.13548</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>638</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -2393,20 +2741,30 @@
           <t>91 JOSE IGNACIO MIRANDA</t>
         </is>
       </c>
-      <c r="G38" t="n">
-        <v>-15.512981</v>
-      </c>
-      <c r="H38" t="n">
-        <v>-70.12539</v>
-      </c>
-      <c r="I38" t="n">
-        <v>670</v>
-      </c>
-      <c r="J38" t="n">
-        <v>37</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0</v>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>-15.512981</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>-70.12539</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>670</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -2445,20 +2803,30 @@
           <t>CESAR VALLEJO</t>
         </is>
       </c>
-      <c r="G39" t="n">
-        <v>-15.47556</v>
-      </c>
-      <c r="H39" t="n">
-        <v>-70.151276</v>
-      </c>
-      <c r="I39" t="n">
-        <v>708</v>
-      </c>
-      <c r="J39" t="n">
-        <v>45</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0</v>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>-15.47556</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>-70.151276</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>708</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -2497,20 +2865,30 @@
           <t>SAN FRANSISCO DE BORJA</t>
         </is>
       </c>
-      <c r="G40" t="n">
-        <v>-15.49014</v>
-      </c>
-      <c r="H40" t="n">
-        <v>-70.15721000000001</v>
-      </c>
-      <c r="I40" t="n">
-        <v>735</v>
-      </c>
-      <c r="J40" t="n">
-        <v>40</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0</v>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>-15.49014</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>-70.15721</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>735</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -2549,20 +2927,30 @@
           <t>SAN MARTIN</t>
         </is>
       </c>
-      <c r="G41" t="n">
-        <v>-15.47789</v>
-      </c>
-      <c r="H41" t="n">
-        <v>-70.10889</v>
-      </c>
-      <c r="I41" t="n">
-        <v>1534</v>
-      </c>
-      <c r="J41" t="n">
-        <v>105</v>
-      </c>
-      <c r="K41" t="n">
-        <v>0</v>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>-15.47789</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>-70.10889</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1534</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -2601,20 +2989,30 @@
           <t>70708 COLIBRI / COLIBRI</t>
         </is>
       </c>
-      <c r="G42" t="n">
-        <v>-15.49521</v>
-      </c>
-      <c r="H42" t="n">
-        <v>-70.12806999999999</v>
-      </c>
-      <c r="I42" t="n">
-        <v>362</v>
-      </c>
-      <c r="J42" t="n">
-        <v>20</v>
-      </c>
-      <c r="K42" t="n">
-        <v>0</v>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>-15.49521</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>-70.12807</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>362</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -2653,20 +3051,30 @@
           <t>JAMES BALDWIN</t>
         </is>
       </c>
-      <c r="G43" t="n">
-        <v>-15.4905</v>
-      </c>
-      <c r="H43" t="n">
-        <v>-70.12990000000001</v>
-      </c>
-      <c r="I43" t="n">
-        <v>1008</v>
-      </c>
-      <c r="J43" t="n">
-        <v>51</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0</v>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>-15.4905</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>-70.1299</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1008</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -2705,20 +3113,30 @@
           <t>DANIELLE MITTERRAND</t>
         </is>
       </c>
-      <c r="G44" t="n">
-        <v>-15.49684</v>
-      </c>
-      <c r="H44" t="n">
-        <v>-70.13333</v>
-      </c>
-      <c r="I44" t="n">
-        <v>952</v>
-      </c>
-      <c r="J44" t="n">
-        <v>54</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0</v>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>-15.49684</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>-70.13333</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>952</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -2757,20 +3175,30 @@
           <t>SANTA CATALINA</t>
         </is>
       </c>
-      <c r="G45" t="n">
-        <v>-15.49548</v>
-      </c>
-      <c r="H45" t="n">
-        <v>-70.13702000000001</v>
-      </c>
-      <c r="I45" t="n">
-        <v>1176</v>
-      </c>
-      <c r="J45" t="n">
-        <v>44</v>
-      </c>
-      <c r="K45" t="n">
-        <v>0</v>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>-15.49548</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>-70.13702</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1176</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -2809,20 +3237,30 @@
           <t>LUZ ANDINA / LUZ ANDINA REYNA DE LAS AMERICAS</t>
         </is>
       </c>
-      <c r="G46" t="n">
-        <v>-15.49249</v>
-      </c>
-      <c r="H46" t="n">
-        <v>-70.1284</v>
-      </c>
-      <c r="I46" t="n">
-        <v>547</v>
-      </c>
-      <c r="J46" t="n">
-        <v>44</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0</v>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>-15.49249</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>-70.1284</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>547</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -2861,20 +3299,30 @@
           <t>SAN JOSE LA ESPERANZA</t>
         </is>
       </c>
-      <c r="G47" t="n">
-        <v>-15.49779</v>
-      </c>
-      <c r="H47" t="n">
-        <v>-70.13357999999999</v>
-      </c>
-      <c r="I47" t="n">
-        <v>288</v>
-      </c>
-      <c r="J47" t="n">
-        <v>27</v>
-      </c>
-      <c r="K47" t="n">
-        <v>0</v>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>-15.49779</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>-70.13358</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -2913,20 +3361,30 @@
           <t>BETHEL CHRISTIAN SCHOOL</t>
         </is>
       </c>
-      <c r="G48" t="n">
-        <v>-15.4884</v>
-      </c>
-      <c r="H48" t="n">
-        <v>-70.12888</v>
-      </c>
-      <c r="I48" t="n">
-        <v>272</v>
-      </c>
-      <c r="J48" t="n">
-        <v>21</v>
-      </c>
-      <c r="K48" t="n">
-        <v>0</v>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>-15.4884</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>-70.12888</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
@@ -2965,20 +3423,30 @@
           <t>PEDRO KALBERMATTER</t>
         </is>
       </c>
-      <c r="G49" t="n">
-        <v>-15.49053</v>
-      </c>
-      <c r="H49" t="n">
-        <v>-70.14364999999999</v>
-      </c>
-      <c r="I49" t="n">
-        <v>342</v>
-      </c>
-      <c r="J49" t="n">
-        <v>30</v>
-      </c>
-      <c r="K49" t="n">
-        <v>0</v>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>-15.49053</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>-70.14365</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>342</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -3017,20 +3485,30 @@
           <t>AMERICANA</t>
         </is>
       </c>
-      <c r="G50" t="n">
-        <v>-15.49934</v>
-      </c>
-      <c r="H50" t="n">
-        <v>-70.13432</v>
-      </c>
-      <c r="I50" t="n">
-        <v>619</v>
-      </c>
-      <c r="J50" t="n">
-        <v>34</v>
-      </c>
-      <c r="K50" t="n">
-        <v>0</v>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>-15.49934</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>-70.13432</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>619</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
@@ -3069,20 +3547,30 @@
           <t>TUPAC AMARU</t>
         </is>
       </c>
-      <c r="G51" t="n">
-        <v>-15.49024</v>
-      </c>
-      <c r="H51" t="n">
-        <v>-70.12615</v>
-      </c>
-      <c r="I51" t="n">
-        <v>1291</v>
-      </c>
-      <c r="J51" t="n">
-        <v>61</v>
-      </c>
-      <c r="K51" t="n">
-        <v>0</v>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>-15.49024</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>-70.12615</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1291</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
@@ -3121,20 +3609,30 @@
           <t>FRANCISCANO SAN ROMAN</t>
         </is>
       </c>
-      <c r="G52" t="n">
-        <v>-15.49307</v>
-      </c>
-      <c r="H52" t="n">
-        <v>-70.13621999999999</v>
-      </c>
-      <c r="I52" t="n">
-        <v>862</v>
-      </c>
-      <c r="J52" t="n">
-        <v>38</v>
-      </c>
-      <c r="K52" t="n">
-        <v>1</v>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>-15.49307</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>-70.13622</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>862</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
@@ -3173,20 +3671,30 @@
           <t>ADVENTISTA DEL TITICACA</t>
         </is>
       </c>
-      <c r="G53" t="n">
-        <v>-15.51645</v>
-      </c>
-      <c r="H53" t="n">
-        <v>-70.179603</v>
-      </c>
-      <c r="I53" t="n">
-        <v>1192</v>
-      </c>
-      <c r="J53" t="n">
-        <v>70</v>
-      </c>
-      <c r="K53" t="n">
-        <v>0</v>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>-15.51645</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>-70.179603</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1192</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
@@ -3225,20 +3733,30 @@
           <t>BELEN</t>
         </is>
       </c>
-      <c r="G54" t="n">
-        <v>-15.48461</v>
-      </c>
-      <c r="H54" t="n">
-        <v>-70.1326</v>
-      </c>
-      <c r="I54" t="n">
-        <v>259</v>
-      </c>
-      <c r="J54" t="n">
-        <v>21</v>
-      </c>
-      <c r="K54" t="n">
-        <v>0</v>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>-15.48461</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>-70.1326</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>259</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
@@ -3277,20 +3795,30 @@
           <t>FERNANDO STAHL</t>
         </is>
       </c>
-      <c r="G55" t="n">
-        <v>-15.49929</v>
-      </c>
-      <c r="H55" t="n">
-        <v>-70.12626</v>
-      </c>
-      <c r="I55" t="n">
-        <v>818</v>
-      </c>
-      <c r="J55" t="n">
-        <v>44</v>
-      </c>
-      <c r="K55" t="n">
-        <v>1</v>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>-15.49929</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>-70.12626</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>818</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
@@ -3329,20 +3857,30 @@
           <t>BUEN PASTOR</t>
         </is>
       </c>
-      <c r="G56" t="n">
-        <v>-15.49303</v>
-      </c>
-      <c r="H56" t="n">
-        <v>-70.12990000000001</v>
-      </c>
-      <c r="I56" t="n">
-        <v>564</v>
-      </c>
-      <c r="J56" t="n">
-        <v>37</v>
-      </c>
-      <c r="K56" t="n">
-        <v>1</v>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>-15.49303</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>-70.1299</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>564</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
@@ -3381,20 +3919,30 @@
           <t>SAGRADO CORAZON DE JESUS</t>
         </is>
       </c>
-      <c r="G57" t="n">
-        <v>-15.49045</v>
-      </c>
-      <c r="H57" t="n">
-        <v>-70.13261</v>
-      </c>
-      <c r="I57" t="n">
-        <v>351</v>
-      </c>
-      <c r="J57" t="n">
-        <v>29</v>
-      </c>
-      <c r="K57" t="n">
-        <v>0</v>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>-15.49045</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>-70.13261</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>351</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
@@ -3433,20 +3981,30 @@
           <t>ANTONIO RAYMONDI / ANTONIO RAYMONDY</t>
         </is>
       </c>
-      <c r="G58" t="n">
-        <v>-15.49209</v>
-      </c>
-      <c r="H58" t="n">
-        <v>-70.12533999999999</v>
-      </c>
-      <c r="I58" t="n">
-        <v>285</v>
-      </c>
-      <c r="J58" t="n">
-        <v>16</v>
-      </c>
-      <c r="K58" t="n">
-        <v>0</v>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>-15.49209</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>-70.12534</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
@@ -3485,20 +4043,30 @@
           <t>MARISCAL ANDRES AVELINO CACERES</t>
         </is>
       </c>
-      <c r="G59" t="n">
-        <v>-15.48467</v>
-      </c>
-      <c r="H59" t="n">
-        <v>-70.15335</v>
-      </c>
-      <c r="I59" t="n">
-        <v>126</v>
-      </c>
-      <c r="J59" t="n">
-        <v>20</v>
-      </c>
-      <c r="K59" t="n">
-        <v>1</v>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>-15.48467</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>-70.15335</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
@@ -3537,20 +4105,30 @@
           <t>MARCELINO CHAMPAGNAT</t>
         </is>
       </c>
-      <c r="G60" t="n">
-        <v>-15.4923</v>
-      </c>
-      <c r="H60" t="n">
-        <v>-70.13065</v>
-      </c>
-      <c r="I60" t="n">
-        <v>118</v>
-      </c>
-      <c r="J60" t="n">
-        <v>25</v>
-      </c>
-      <c r="K60" t="n">
-        <v>1</v>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>-15.4923</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>-70.13065</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
@@ -3589,20 +4167,30 @@
           <t>TRINOMIO</t>
         </is>
       </c>
-      <c r="G61" t="n">
-        <v>-15.48886</v>
-      </c>
-      <c r="H61" t="n">
-        <v>-70.12824000000001</v>
-      </c>
-      <c r="I61" t="n">
-        <v>613</v>
-      </c>
-      <c r="J61" t="n">
-        <v>28</v>
-      </c>
-      <c r="K61" t="n">
-        <v>0</v>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>-15.48886</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>-70.12824</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>613</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
@@ -3641,20 +4229,30 @@
           <t>LUZ Y CIENCIA</t>
         </is>
       </c>
-      <c r="G62" t="n">
-        <v>-15.49299</v>
-      </c>
-      <c r="H62" t="n">
-        <v>-70.13381</v>
-      </c>
-      <c r="I62" t="n">
-        <v>318</v>
-      </c>
-      <c r="J62" t="n">
-        <v>21</v>
-      </c>
-      <c r="K62" t="n">
-        <v>0</v>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>-15.49299</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>-70.13381</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>318</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
@@ -3693,20 +4291,30 @@
           <t>1139 / 70538</t>
         </is>
       </c>
-      <c r="G63" t="n">
-        <v>-15.56746</v>
-      </c>
-      <c r="H63" t="n">
-        <v>-70.10044000000001</v>
-      </c>
-      <c r="I63" t="n">
-        <v>290</v>
-      </c>
-      <c r="J63" t="n">
-        <v>16</v>
-      </c>
-      <c r="K63" t="n">
-        <v>0</v>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>-15.56746</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>-70.10044</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
@@ -3745,20 +4353,30 @@
           <t>SIGMA</t>
         </is>
       </c>
-      <c r="G64" t="n">
-        <v>-15.48973</v>
-      </c>
-      <c r="H64" t="n">
-        <v>-70.12839</v>
-      </c>
-      <c r="I64" t="n">
-        <v>504</v>
-      </c>
-      <c r="J64" t="n">
-        <v>31</v>
-      </c>
-      <c r="K64" t="n">
-        <v>0</v>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>-15.48973</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>-70.12839</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>504</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
@@ -3797,20 +4415,30 @@
           <t>NUEVO HORIZONTE</t>
         </is>
       </c>
-      <c r="G65" t="n">
-        <v>-15.48828</v>
-      </c>
-      <c r="H65" t="n">
-        <v>-70.11967</v>
-      </c>
-      <c r="I65" t="n">
-        <v>326</v>
-      </c>
-      <c r="J65" t="n">
-        <v>20</v>
-      </c>
-      <c r="K65" t="n">
-        <v>0</v>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>-15.48828</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>-70.11967</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>326</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
@@ -3849,20 +4477,30 @@
           <t>MARTIN LUTERO</t>
         </is>
       </c>
-      <c r="G66" t="n">
-        <v>-15.5103</v>
-      </c>
-      <c r="H66" t="n">
-        <v>-70.11705000000001</v>
-      </c>
-      <c r="I66" t="n">
-        <v>509</v>
-      </c>
-      <c r="J66" t="n">
-        <v>23</v>
-      </c>
-      <c r="K66" t="n">
-        <v>0</v>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>-15.5103</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>-70.11705</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>509</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
@@ -3901,20 +4539,30 @@
           <t>ENRIQUE GUZMAN Y VALLE</t>
         </is>
       </c>
-      <c r="G67" t="n">
-        <v>-15.49327</v>
-      </c>
-      <c r="H67" t="n">
-        <v>-70.12626</v>
-      </c>
-      <c r="I67" t="n">
-        <v>333</v>
-      </c>
-      <c r="J67" t="n">
-        <v>26</v>
-      </c>
-      <c r="K67" t="n">
-        <v>0</v>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>-15.49327</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>-70.12626</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>333</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
@@ -3953,20 +4601,30 @@
           <t>ASOCIACION EDUCATIVA ADVENTISTA CRISTO REY</t>
         </is>
       </c>
-      <c r="G68" t="n">
-        <v>-15.4899</v>
-      </c>
-      <c r="H68" t="n">
-        <v>-70.12142</v>
-      </c>
-      <c r="I68" t="n">
-        <v>226</v>
-      </c>
-      <c r="J68" t="n">
-        <v>19</v>
-      </c>
-      <c r="K68" t="n">
-        <v>0</v>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>-15.4899</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>-70.12142</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
@@ -4005,20 +4663,30 @@
           <t>BILINGÜE PERUANO ESPAÑOL</t>
         </is>
       </c>
-      <c r="G69" t="n">
-        <v>-15.48268</v>
-      </c>
-      <c r="H69" t="n">
-        <v>-70.13806</v>
-      </c>
-      <c r="I69" t="n">
-        <v>208</v>
-      </c>
-      <c r="J69" t="n">
-        <v>11</v>
-      </c>
-      <c r="K69" t="n">
-        <v>0</v>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>-15.48268</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>-70.13806</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
@@ -4057,20 +4725,30 @@
           <t>989</t>
         </is>
       </c>
-      <c r="G70" t="n">
-        <v>-15.49285</v>
-      </c>
-      <c r="H70" t="n">
-        <v>-70.11608</v>
-      </c>
-      <c r="I70" t="n">
-        <v>36</v>
-      </c>
-      <c r="J70" t="n">
-        <v>2</v>
-      </c>
-      <c r="K70" t="n">
-        <v>1</v>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>-15.49285</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>-70.11608</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
@@ -4109,20 +4787,30 @@
           <t>LIDER</t>
         </is>
       </c>
-      <c r="G71" t="n">
-        <v>-15.48845</v>
-      </c>
-      <c r="H71" t="n">
-        <v>-70.11766</v>
-      </c>
-      <c r="I71" t="n">
-        <v>535</v>
-      </c>
-      <c r="J71" t="n">
-        <v>30</v>
-      </c>
-      <c r="K71" t="n">
-        <v>0</v>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>-15.48845</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>-70.11766</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>535</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
@@ -4161,20 +4849,30 @@
           <t>307 CONRADO KRETZ LENZ</t>
         </is>
       </c>
-      <c r="G72" t="n">
-        <v>-15.48151</v>
-      </c>
-      <c r="H72" t="n">
-        <v>-70.12682</v>
-      </c>
-      <c r="I72" t="n">
-        <v>299</v>
-      </c>
-      <c r="J72" t="n">
-        <v>13</v>
-      </c>
-      <c r="K72" t="n">
-        <v>0</v>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>-15.48151</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>-70.12682</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>299</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
@@ -4213,20 +4911,30 @@
           <t>MARISCAL ANDRES AVELINO CACERES</t>
         </is>
       </c>
-      <c r="G73" t="n">
-        <v>-15.48477</v>
-      </c>
-      <c r="H73" t="n">
-        <v>-70.1529</v>
-      </c>
-      <c r="I73" t="n">
-        <v>14</v>
-      </c>
-      <c r="J73" t="n">
-        <v>3</v>
-      </c>
-      <c r="K73" t="n">
-        <v>1</v>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>-15.48477</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>-70.1529</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
@@ -4265,20 +4973,30 @@
           <t>PITAGORAS</t>
         </is>
       </c>
-      <c r="G74" t="n">
-        <v>-15.49336</v>
-      </c>
-      <c r="H74" t="n">
-        <v>-70.1374</v>
-      </c>
-      <c r="I74" t="n">
-        <v>69</v>
-      </c>
-      <c r="J74" t="n">
-        <v>4</v>
-      </c>
-      <c r="K74" t="n">
-        <v>1</v>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>-15.49336</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>-70.1374</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
@@ -4317,20 +5035,30 @@
           <t>SANTA MONICA</t>
         </is>
       </c>
-      <c r="G75" t="n">
-        <v>-15.49995</v>
-      </c>
-      <c r="H75" t="n">
-        <v>-70.15262</v>
-      </c>
-      <c r="I75" t="n">
-        <v>512</v>
-      </c>
-      <c r="J75" t="n">
-        <v>28</v>
-      </c>
-      <c r="K75" t="n">
-        <v>0</v>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>-15.49995</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-70.15262</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>512</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
@@ -4369,20 +5097,30 @@
           <t>RODOLFO DIESEL</t>
         </is>
       </c>
-      <c r="G76" t="n">
-        <v>-15.45792</v>
-      </c>
-      <c r="H76" t="n">
-        <v>-70.146126</v>
-      </c>
-      <c r="I76" t="n">
-        <v>503</v>
-      </c>
-      <c r="J76" t="n">
-        <v>25</v>
-      </c>
-      <c r="K76" t="n">
-        <v>0</v>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>-15.45792</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>-70.146126</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>503</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
@@ -4421,20 +5159,30 @@
           <t>ELENA DE SANTA MARIA</t>
         </is>
       </c>
-      <c r="G77" t="n">
-        <v>-15.52179</v>
-      </c>
-      <c r="H77" t="n">
-        <v>-70.12515999999999</v>
-      </c>
-      <c r="I77" t="n">
-        <v>554</v>
-      </c>
-      <c r="J77" t="n">
-        <v>51</v>
-      </c>
-      <c r="K77" t="n">
-        <v>0</v>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>-15.52179</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>-70.12516</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>554</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
@@ -4473,20 +5221,30 @@
           <t>1144</t>
         </is>
       </c>
-      <c r="G78" t="n">
-        <v>-15.47207</v>
-      </c>
-      <c r="H78" t="n">
-        <v>-70.11042</v>
-      </c>
-      <c r="I78" t="n">
-        <v>17</v>
-      </c>
-      <c r="J78" t="n">
-        <v>1</v>
-      </c>
-      <c r="K78" t="n">
-        <v>1</v>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>-15.47207</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>-70.11042</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
@@ -4525,20 +5283,30 @@
           <t>LA SALLE</t>
         </is>
       </c>
-      <c r="G79" t="n">
-        <v>-15.50171</v>
-      </c>
-      <c r="H79" t="n">
-        <v>-70.13281000000001</v>
-      </c>
-      <c r="I79" t="n">
-        <v>243</v>
-      </c>
-      <c r="J79" t="n">
-        <v>21</v>
-      </c>
-      <c r="K79" t="n">
-        <v>0</v>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>-15.50171</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>-70.13281</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
@@ -4577,20 +5345,30 @@
           <t>JOSE OLAYA BALANDRA</t>
         </is>
       </c>
-      <c r="G80" t="n">
-        <v>-15.436401</v>
-      </c>
-      <c r="H80" t="n">
-        <v>-70.146474</v>
-      </c>
-      <c r="I80" t="n">
-        <v>233</v>
-      </c>
-      <c r="J80" t="n">
-        <v>14</v>
-      </c>
-      <c r="K80" t="n">
-        <v>0</v>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>-15.436401</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>-70.146474</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
@@ -4629,20 +5407,30 @@
           <t>INTERNATIONAL PERUVIAN SCHOOL</t>
         </is>
       </c>
-      <c r="G81" t="n">
-        <v>-15.46999</v>
-      </c>
-      <c r="H81" t="n">
-        <v>-70.14085</v>
-      </c>
-      <c r="I81" t="n">
-        <v>299</v>
-      </c>
-      <c r="J81" t="n">
-        <v>19</v>
-      </c>
-      <c r="K81" t="n">
-        <v>1</v>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>-15.46999</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>-70.14085</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>299</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
@@ -4681,20 +5469,30 @@
           <t>1361 SAN JACINTO</t>
         </is>
       </c>
-      <c r="G82" t="n">
-        <v>-15.49313</v>
-      </c>
-      <c r="H82" t="n">
-        <v>-70.11756</v>
-      </c>
-      <c r="I82" t="n">
-        <v>10</v>
-      </c>
-      <c r="J82" t="n">
-        <v>1</v>
-      </c>
-      <c r="K82" t="n">
-        <v>1</v>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>-15.49313</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>-70.11756</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
@@ -4733,20 +5531,30 @@
           <t>BRITANICO SCHOOL</t>
         </is>
       </c>
-      <c r="G83" t="n">
-        <v>-15.49286</v>
-      </c>
-      <c r="H83" t="n">
-        <v>-70.14694</v>
-      </c>
-      <c r="I83" t="n">
-        <v>47</v>
-      </c>
-      <c r="J83" t="n">
-        <v>4</v>
-      </c>
-      <c r="K83" t="n">
-        <v>1</v>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>-15.49286</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>-70.14694</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
@@ -4785,20 +5593,30 @@
           <t>ANDRES BELLO</t>
         </is>
       </c>
-      <c r="G84" t="n">
-        <v>-15.48786</v>
-      </c>
-      <c r="H84" t="n">
-        <v>-70.12751</v>
-      </c>
-      <c r="I84" t="n">
-        <v>261</v>
-      </c>
-      <c r="J84" t="n">
-        <v>20</v>
-      </c>
-      <c r="K84" t="n">
-        <v>0</v>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>-15.48786</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>-70.12751</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
@@ -4837,20 +5655,30 @@
           <t>CLAUDIO GALENO</t>
         </is>
       </c>
-      <c r="G85" t="n">
-        <v>-15.49659</v>
-      </c>
-      <c r="H85" t="n">
-        <v>-70.13258</v>
-      </c>
-      <c r="I85" t="n">
-        <v>843</v>
-      </c>
-      <c r="J85" t="n">
-        <v>35</v>
-      </c>
-      <c r="K85" t="n">
-        <v>0</v>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>-15.49659</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>-70.13258</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>843</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
@@ -4889,20 +5717,30 @@
           <t>GREGOR MENDEL</t>
         </is>
       </c>
-      <c r="G86" t="n">
-        <v>-15.496383</v>
-      </c>
-      <c r="H86" t="n">
-        <v>-70.127776</v>
-      </c>
-      <c r="I86" t="n">
-        <v>355</v>
-      </c>
-      <c r="J86" t="n">
-        <v>26</v>
-      </c>
-      <c r="K86" t="n">
-        <v>0</v>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>-15.496383</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>-70.127776</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>355</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
@@ -4941,20 +5779,30 @@
           <t>CLAUDIO GALENO</t>
         </is>
       </c>
-      <c r="G87" t="n">
-        <v>-15.49659</v>
-      </c>
-      <c r="H87" t="n">
-        <v>-70.1326</v>
-      </c>
-      <c r="I87" t="n">
-        <v>370</v>
-      </c>
-      <c r="J87" t="n">
-        <v>15</v>
-      </c>
-      <c r="K87" t="n">
-        <v>0</v>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>-15.49659</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>-70.1326</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>370</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
@@ -4993,20 +5841,30 @@
           <t>MIGUEL GRAU</t>
         </is>
       </c>
-      <c r="G88" t="n">
-        <v>-15.50331</v>
-      </c>
-      <c r="H88" t="n">
-        <v>-70.12155</v>
-      </c>
-      <c r="I88" t="n">
-        <v>259</v>
-      </c>
-      <c r="J88" t="n">
-        <v>21</v>
-      </c>
-      <c r="K88" t="n">
-        <v>0</v>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>-15.50331</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>-70.12155</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>259</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
@@ -5045,20 +5903,30 @@
           <t>GIORDANO LIVA</t>
         </is>
       </c>
-      <c r="G89" t="n">
-        <v>-15.51137</v>
-      </c>
-      <c r="H89" t="n">
-        <v>-70.122643</v>
-      </c>
-      <c r="I89" t="n">
-        <v>222</v>
-      </c>
-      <c r="J89" t="n">
-        <v>24</v>
-      </c>
-      <c r="K89" t="n">
-        <v>0</v>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>-15.51137</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>-70.122643</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
@@ -5097,20 +5965,30 @@
           <t>FE Y CIENCIA</t>
         </is>
       </c>
-      <c r="G90" t="n">
-        <v>-15.451127</v>
-      </c>
-      <c r="H90" t="n">
-        <v>-70.14129</v>
-      </c>
-      <c r="I90" t="n">
-        <v>202</v>
-      </c>
-      <c r="J90" t="n">
-        <v>18</v>
-      </c>
-      <c r="K90" t="n">
-        <v>0</v>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>-15.451127</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>-70.14129</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
@@ -5149,20 +6027,30 @@
           <t>THOMAS CRANMER</t>
         </is>
       </c>
-      <c r="G91" t="n">
-        <v>-15.4867</v>
-      </c>
-      <c r="H91" t="n">
-        <v>-70.133</v>
-      </c>
-      <c r="I91" t="n">
-        <v>253</v>
-      </c>
-      <c r="J91" t="n">
-        <v>11</v>
-      </c>
-      <c r="K91" t="n">
-        <v>0</v>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>-15.4867</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>-70.133</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
@@ -5201,20 +6089,30 @@
           <t>REAL AMERICAN SCHOOL</t>
         </is>
       </c>
-      <c r="G92" t="n">
-        <v>-15.4828</v>
-      </c>
-      <c r="H92" t="n">
-        <v>-70.13809000000001</v>
-      </c>
-      <c r="I92" t="n">
-        <v>335</v>
-      </c>
-      <c r="J92" t="n">
-        <v>14</v>
-      </c>
-      <c r="K92" t="n">
-        <v>0</v>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>-15.4828</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>-70.13809</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>335</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
@@ -5253,20 +6151,30 @@
           <t>PACIFIC SCHOOL</t>
         </is>
       </c>
-      <c r="G93" t="n">
-        <v>-15.494</v>
-      </c>
-      <c r="H93" t="n">
-        <v>-70.13639999999999</v>
-      </c>
-      <c r="I93" t="n">
-        <v>15</v>
-      </c>
-      <c r="J93" t="n">
-        <v>5</v>
-      </c>
-      <c r="K93" t="n">
-        <v>1</v>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>-15.494</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>-70.1364</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
@@ -5305,20 +6213,30 @@
           <t>GANIMEDES</t>
         </is>
       </c>
-      <c r="G94" t="n">
-        <v>-15.46173</v>
-      </c>
-      <c r="H94" t="n">
-        <v>-70.15136</v>
-      </c>
-      <c r="I94" t="n">
-        <v>218</v>
-      </c>
-      <c r="J94" t="n">
-        <v>21</v>
-      </c>
-      <c r="K94" t="n">
-        <v>0</v>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>-15.46173</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>-70.15136</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
@@ -5357,20 +6275,30 @@
           <t>TALENTOS LIBER</t>
         </is>
       </c>
-      <c r="G95" t="n">
-        <v>-15.49008</v>
-      </c>
-      <c r="H95" t="n">
-        <v>-70.13583</v>
-      </c>
-      <c r="I95" t="n">
-        <v>248</v>
-      </c>
-      <c r="J95" t="n">
-        <v>27</v>
-      </c>
-      <c r="K95" t="n">
-        <v>0</v>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>-15.49008</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>-70.13583</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
@@ -5409,20 +6337,30 @@
           <t>ALPHA INTERNATIONAL SCHOOL</t>
         </is>
       </c>
-      <c r="G96" t="n">
-        <v>-15.51196</v>
-      </c>
-      <c r="H96" t="n">
-        <v>-70.12626</v>
-      </c>
-      <c r="I96" t="n">
-        <v>51</v>
-      </c>
-      <c r="J96" t="n">
-        <v>5</v>
-      </c>
-      <c r="K96" t="n">
-        <v>1</v>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>-15.51196</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>-70.12626</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
@@ -5461,20 +6399,30 @@
           <t>THOMAS ALVA EDISON</t>
         </is>
       </c>
-      <c r="G97" t="n">
-        <v>-15.50134</v>
-      </c>
-      <c r="H97" t="n">
-        <v>-70.115374</v>
-      </c>
-      <c r="I97" t="n">
-        <v>277</v>
-      </c>
-      <c r="J97" t="n">
-        <v>15</v>
-      </c>
-      <c r="K97" t="n">
-        <v>0</v>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>-15.50134</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>-70.115374</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
@@ -5513,20 +6461,30 @@
           <t>INNOVA SCHOOLS - JULIACA</t>
         </is>
       </c>
-      <c r="G98" t="n">
-        <v>-15.51362</v>
-      </c>
-      <c r="H98" t="n">
-        <v>-70.12139999999999</v>
-      </c>
-      <c r="I98" t="n">
-        <v>765</v>
-      </c>
-      <c r="J98" t="n">
-        <v>43</v>
-      </c>
-      <c r="K98" t="n">
-        <v>0</v>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>-15.51362</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>-70.1214</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>765</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
@@ -5565,20 +6523,30 @@
           <t>PITAGORAS</t>
         </is>
       </c>
-      <c r="G99" t="n">
-        <v>-15.493121</v>
-      </c>
-      <c r="H99" t="n">
-        <v>-70.138336</v>
-      </c>
-      <c r="I99" t="n">
-        <v>233</v>
-      </c>
-      <c r="J99" t="n">
-        <v>18</v>
-      </c>
-      <c r="K99" t="n">
-        <v>0</v>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>-15.493121</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>-70.138336</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
@@ -5617,20 +6585,30 @@
           <t>SANTA ROSA DE LIMA</t>
         </is>
       </c>
-      <c r="G100" t="n">
-        <v>-15.5286</v>
-      </c>
-      <c r="H100" t="n">
-        <v>-70.12222</v>
-      </c>
-      <c r="I100" t="n">
-        <v>241</v>
-      </c>
-      <c r="J100" t="n">
-        <v>22</v>
-      </c>
-      <c r="K100" t="n">
-        <v>0</v>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>-15.5286</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>-70.12222</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>241</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
@@ -5669,20 +6647,30 @@
           <t>SAN IGNACIO DE RECALDE</t>
         </is>
       </c>
-      <c r="G101" t="n">
-        <v>-15.48912</v>
-      </c>
-      <c r="H101" t="n">
-        <v>-70.12647</v>
-      </c>
-      <c r="I101" t="n">
-        <v>284</v>
-      </c>
-      <c r="J101" t="n">
-        <v>24</v>
-      </c>
-      <c r="K101" t="n">
-        <v>0</v>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>-15.48912</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>-70.12647</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>284</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
@@ -5721,20 +6709,30 @@
           <t>SAN GINES DE ARLES</t>
         </is>
       </c>
-      <c r="G102" t="n">
-        <v>-15.487268</v>
-      </c>
-      <c r="H102" t="n">
-        <v>-70.132835</v>
-      </c>
-      <c r="I102" t="n">
-        <v>289</v>
-      </c>
-      <c r="J102" t="n">
-        <v>23</v>
-      </c>
-      <c r="K102" t="n">
-        <v>0</v>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>-15.487268</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>-70.132835</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
@@ -5773,20 +6771,30 @@
           <t>ANGELES SCHOOL</t>
         </is>
       </c>
-      <c r="G103" t="n">
-        <v>-15.476925</v>
-      </c>
-      <c r="H103" t="n">
-        <v>-70.115798</v>
-      </c>
-      <c r="I103" t="n">
-        <v>21</v>
-      </c>
-      <c r="J103" t="n">
-        <v>3</v>
-      </c>
-      <c r="K103" t="n">
-        <v>1</v>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>-15.476925</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>-70.115798</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>

--- a/ZonasEscolares/excels/PUNO-SAN_ROMAN-JULIACA.xlsx
+++ b/ZonasEscolares/excels/PUNO-SAN_ROMAN-JULIACA.xlsx
@@ -501,37 +501,37 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>462963</t>
+          <t>742252</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>305</t>
+          <t>1144</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-15.49314</t>
+          <t>-15.47207</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-70.13194</t>
+          <t>-70.11042</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>459</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -563,37 +563,37 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>462977</t>
+          <t>762693</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>306 BARCIA BONIFFATI</t>
+          <t>1361 SAN JACINTO</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-15.4889</t>
+          <t>-15.49313</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-70.13864</t>
+          <t>-70.11756</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>462996</t>
+          <t>464014</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>308 NIÑO JESUS DE PRAGA</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-15.5023</t>
+          <t>-15.47789</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-70.1267</t>
+          <t>-70.10889</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>245</t>
+          <t>1534</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>105</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>463024</t>
+          <t>462977</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>314</t>
+          <t>306 BARCIA BONIFFATI</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-15.48499</t>
+          <t>-15.4889</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-70.14094</t>
+          <t>-70.13864</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>396</t>
+          <t>261</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>463302</t>
+          <t>624569</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>70536</t>
+          <t>BILINGÜE PERUANO ESPAÑOL</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-15.487922</t>
+          <t>-15.48268</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-70.146288</t>
+          <t>-70.13806</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>840</t>
+          <t>208</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>463316</t>
+          <t>837090</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>70541 VIRGEN DE FATIMA</t>
+          <t>THOMAS CRANMER</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-15.4931</t>
+          <t>-15.4867</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-70.13178</t>
+          <t>-70.133</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>830</t>
+          <t>253</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>463321</t>
+          <t>462996</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>70542</t>
+          <t>308 NIÑO JESUS DE PRAGA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-15.489797</t>
+          <t>-15.5023</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-70.138508</t>
+          <t>-70.1267</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>245</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>463335</t>
+          <t>463439</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>70545 TUPAC AMARU</t>
+          <t>70560 SEÑOR DE LOS MILAGROS</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-15.48968</t>
+          <t>-15.49694</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-70.127713</t>
+          <t>-70.1267</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>764</t>
+          <t>239</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -970,7 +970,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>463340</t>
+          <t>693162</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>70546 SEÑOR DE HUANCA</t>
+          <t>307 CONRADO KRETZ LENZ</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-15.50498</t>
+          <t>-15.48151</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-70.12675</t>
+          <t>-70.12682</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>710</t>
+          <t>299</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>463359</t>
+          <t>463910</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>70547</t>
+          <t>JOSE ANTONIO ENCINAS</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-15.484065</t>
+          <t>-15.487692</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-70.128818</t>
+          <t>-70.124215</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>865</t>
+          <t>2807</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>131</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>463364</t>
+          <t>745316</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>70548</t>
+          <t>JOSE OLAYA BALANDRA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-15.49226</t>
+          <t>-15.436401</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-70.14352</t>
+          <t>-70.146474</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>233</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>463378</t>
+          <t>840021</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>70549 VIRGEN DEL CARMEN</t>
+          <t>REAL AMERICAN SCHOOL</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-15.48992</t>
+          <t>-15.4828</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-70.15561</t>
+          <t>-70.13809</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>523</t>
+          <t>335</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>463383</t>
+          <t>463707</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>70550 LOS LIBERTADORES</t>
+          <t>70612</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-15.486474</t>
+          <t>-15.49005</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-70.121435</t>
+          <t>-70.11624</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1312</t>
+          <t>294</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1280,7 +1280,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>463420</t>
+          <t>794910</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>70558</t>
+          <t>CLAUDIO GALENO</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-15.49349</t>
+          <t>-15.49659</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-70.12271</t>
+          <t>-70.1326</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>487</t>
+          <t>370</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>463439</t>
+          <t>855178</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>70560 SEÑOR DE LOS MILAGROS</t>
+          <t>THOMAS ALVA EDISON</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-15.49694</t>
+          <t>-15.50134</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-70.1267</t>
+          <t>-70.115374</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>277</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>463444</t>
+          <t>464410</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>70561</t>
+          <t>ANTONIO RAYMONDI / ANTONIO RAYMONDY</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-15.49782</t>
+          <t>-15.49209</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-70.12072</t>
+          <t>-70.12534</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>524</t>
+          <t>285</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>463458</t>
+          <t>465141</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>70563 NUESTRA SEÑORA DEL CARMEN</t>
+          <t>1139 / 70538</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-15.49952</t>
+          <t>-15.56746</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-70.14198</t>
+          <t>-70.10044</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>422</t>
+          <t>290</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>463463</t>
+          <t>462963</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>70564</t>
+          <t>305</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-15.48484</t>
+          <t>-15.49314</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-70.1398</t>
+          <t>-70.13194</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1002</t>
+          <t>459</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>463477</t>
+          <t>463024</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>70565 MARIANO NUÑEZ</t>
+          <t>314</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-15.49028</t>
+          <t>-15.48499</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-70.13373</t>
+          <t>-70.14094</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>914</t>
+          <t>396</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>463552</t>
+          <t>831074</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>70576 MARISCAL JOSE DE SUCRE</t>
+          <t>FE Y CIENCIA</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-15.48838</t>
+          <t>-15.451127</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-70.13057</t>
+          <t>-70.14129</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>202</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>463670</t>
+          <t>857907</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>70607 JOSE BERNARDO ALCEDO RELUERTO</t>
+          <t>PITAGORAS</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-15.47822</t>
+          <t>-15.493121</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-70.10937</t>
+          <t>-70.138336</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>543</t>
+          <t>233</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>463689</t>
+          <t>539284</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>70610</t>
+          <t>ASOCIACION EDUCATIVA ADVENTISTA CRISTO REY</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-15.48097</t>
+          <t>-15.4899</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-70.15193</t>
+          <t>-70.12142</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>634</t>
+          <t>226</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1865,37 +1865,37 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>463707</t>
+          <t>748329</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>70612</t>
+          <t>INTERNATIONAL PERUVIAN SCHOOL</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-15.49005</t>
+          <t>-15.46999</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-70.11624</t>
+          <t>-70.14085</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>294</t>
+          <t>299</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -1927,37 +1927,37 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>463731</t>
+          <t>690314</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>70615</t>
+          <t>989</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-15.47948</t>
+          <t>-15.49285</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-70.14709</t>
+          <t>-70.11608</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>398</t>
+          <t>36</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>463750</t>
+          <t>464108</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>70617 CESAR VALLEJO</t>
+          <t>70708 COLIBRI / COLIBRI</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-15.47465</t>
+          <t>-15.49521</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-70.11238</t>
+          <t>-70.12807</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>362</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2051,37 +2051,37 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>463774</t>
+          <t>464467</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>70619</t>
+          <t>MARISCAL ANDRES AVELINO CACERES</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-15.48494</t>
+          <t>-15.48467</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-70.11835</t>
+          <t>-70.15335</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>493</t>
+          <t>126</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>463788</t>
+          <t>512246</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>70620</t>
+          <t>NUEVO HORIZONTE</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-15.47849</t>
+          <t>-15.48828</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-70.13844</t>
+          <t>-70.11967</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>708</t>
+          <t>326</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2175,32 +2175,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>463825</t>
+          <t>794340</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>70663 CARLOS DANTE NAVA SILVA</t>
+          <t>ANDRES BELLO</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-15.479091</t>
+          <t>-15.48786</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-70.115599</t>
+          <t>-70.12751</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>514</t>
+          <t>261</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>463873</t>
+          <t>463444</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>71014 MANUEL NUÑEZ BUTRON</t>
+          <t>70561</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-15.499647</t>
+          <t>-15.49782</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-70.131946</t>
+          <t>-70.12072</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1384</t>
+          <t>524</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2299,32 +2299,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>463887</t>
+          <t>463731</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>71015 SAN JUAN BOSCO</t>
+          <t>70615</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-15.49137</t>
+          <t>-15.47948</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-70.13106</t>
+          <t>-70.14709</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1174</t>
+          <t>398</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2334,7 +2334,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>463892</t>
+          <t>463774</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>71016 MARIA AUXILIADORA</t>
+          <t>70619</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-15.49429</t>
+          <t>-15.48494</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-70.13477</t>
+          <t>-70.11835</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1522</t>
+          <t>493</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2396,7 +2396,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2423,32 +2423,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>463905</t>
+          <t>463825</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>LAS MERCEDES</t>
+          <t>70663 CARLOS DANTE NAVA SILVA</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-15.490577</t>
+          <t>-15.479091</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-70.139012</t>
+          <t>-70.115599</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1990</t>
+          <t>514</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2458,7 +2458,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2485,32 +2485,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>463910</t>
+          <t>464250</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>JOSE ANTONIO ENCINAS</t>
+          <t>BETHEL CHRISTIAN SCHOOL</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-15.487692</t>
+          <t>-15.4884</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-70.124215</t>
+          <t>-70.12888</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2807</t>
+          <t>272</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2547,32 +2547,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>463934</t>
+          <t>464349</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>POLITECNICO REGIONAL LOS ANDES</t>
+          <t>BELEN</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-15.488678</t>
+          <t>-15.48461</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-70.143998</t>
+          <t>-70.1326</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2127</t>
+          <t>259</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2609,32 +2609,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>463948</t>
+          <t>464783</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>32 MARIANO H. CORNEJO</t>
+          <t>LUZ Y CIENCIA</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-15.50433</t>
+          <t>-15.49299</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-70.12706</t>
+          <t>-70.13381</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1952</t>
+          <t>318</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2671,32 +2671,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>463953</t>
+          <t>743553</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>JOSE MARIA ARGUEDAS</t>
+          <t>LA SALLE</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-15.50469</t>
+          <t>-15.50171</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-70.13548</t>
+          <t>-70.13281</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>243</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2733,32 +2733,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>463967</t>
+          <t>803721</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>91 JOSE IGNACIO MIRANDA</t>
+          <t>MIGUEL GRAU</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-15.512981</t>
+          <t>-15.50331</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-70.12539</t>
+          <t>-70.12155</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>259</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2795,32 +2795,32 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>463986</t>
+          <t>844477</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>CESAR VALLEJO</t>
+          <t>GANIMEDES</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-15.47556</t>
+          <t>-15.46173</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-70.151276</t>
+          <t>-70.15136</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>708</t>
+          <t>218</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2857,32 +2857,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>463991</t>
+          <t>463458</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>SAN FRANSISCO DE BORJA</t>
+          <t>70563 NUESTRA SEÑORA DEL CARMEN</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-15.49014</t>
+          <t>-15.49952</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-70.15721</t>
+          <t>-70.14198</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>422</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>464014</t>
+          <t>858011</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>SAN MARTIN</t>
+          <t>SANTA ROSA DE LIMA</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-15.47789</t>
+          <t>-15.5286</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-70.10889</t>
+          <t>-70.12222</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>1534</t>
+          <t>241</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>464108</t>
+          <t>463420</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>70708 COLIBRI / COLIBRI</t>
+          <t>70558</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-15.49521</t>
+          <t>-15.49349</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-70.12807</t>
+          <t>-70.12271</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>487</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3043,32 +3043,32 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>464151</t>
+          <t>527196</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>JAMES BALDWIN</t>
+          <t>MARTIN LUTERO</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-15.4905</t>
+          <t>-15.5103</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-70.1299</t>
+          <t>-70.11705</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>1008</t>
+          <t>509</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3105,32 +3105,32 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>464165</t>
+          <t>900920</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>DANIELLE MITTERRAND</t>
+          <t>SAN GINES DE ARLES</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-15.49684</t>
+          <t>-15.487268</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>-70.13333</t>
+          <t>-70.132835</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>289</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3167,32 +3167,32 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>464189</t>
+          <t>806625</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>SANTA CATALINA</t>
+          <t>GIORDANO LIVA</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-15.49548</t>
+          <t>-15.51137</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>-70.13702</t>
+          <t>-70.122643</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>1176</t>
+          <t>222</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3229,32 +3229,32 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>464226</t>
+          <t>862386</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>LUZ ANDINA / LUZ ANDINA REYNA DE LAS AMERICAS</t>
+          <t>SAN IGNACIO DE RECALDE</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-15.49249</t>
+          <t>-15.48912</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-70.1284</t>
+          <t>-70.12647</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>547</t>
+          <t>284</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3291,32 +3291,32 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>464231</t>
+          <t>463378</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>SAN JOSE LA ESPERANZA</t>
+          <t>70549 VIRGEN DEL CARMEN</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-15.49779</t>
+          <t>-15.48992</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>-70.13358</t>
+          <t>-70.15561</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>523</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3353,32 +3353,32 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>464250</t>
+          <t>463552</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>BETHEL CHRISTIAN SCHOOL</t>
+          <t>70576 MARISCAL JOSE DE SUCRE</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-15.4884</t>
+          <t>-15.48838</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>-70.12888</t>
+          <t>-70.13057</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>521</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3415,42 +3415,42 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>464274</t>
+          <t>464580</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>PEDRO KALBERMATTER</t>
+          <t>MARCELINO CHAMPAGNAT</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-15.49053</t>
+          <t>-15.4923</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>-70.14365</t>
+          <t>-70.13065</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>342</t>
+          <t>118</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3477,32 +3477,32 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>464288</t>
+          <t>738759</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>AMERICANA</t>
+          <t>RODOLFO DIESEL</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-15.49934</t>
+          <t>-15.45792</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>-70.13432</t>
+          <t>-70.146126</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>619</t>
+          <t>503</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>464293</t>
+          <t>463670</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>TUPAC AMARU</t>
+          <t>70607 JOSE BERNARDO ALCEDO RELUERTO</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-15.49024</t>
+          <t>-15.47822</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>-70.12615</t>
+          <t>-70.10937</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>1291</t>
+          <t>543</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3574,7 +3574,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3601,37 +3601,37 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>464306</t>
+          <t>527865</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>FRANCISCANO SAN ROMAN</t>
+          <t>ENRIQUE GUZMAN Y VALLE</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-15.49307</t>
+          <t>-15.49327</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>-70.13622</t>
+          <t>-70.12626</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>862</t>
+          <t>333</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3663,32 +3663,32 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>464325</t>
+          <t>794745</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>ADVENTISTA DEL TITICACA</t>
+          <t>GREGOR MENDEL</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-15.51645</t>
+          <t>-15.496383</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>-70.179603</t>
+          <t>-70.127776</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>1192</t>
+          <t>355</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3725,32 +3725,32 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>464349</t>
+          <t>464231</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>BELEN</t>
+          <t>SAN JOSE LA ESPERANZA</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-15.48461</t>
+          <t>-15.49779</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>-70.1326</t>
+          <t>-70.13358</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>288</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3787,37 +3787,37 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>464373</t>
+          <t>854503</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>FERNANDO STAHL</t>
+          <t>TALENTOS LIBER</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-15.49929</t>
+          <t>-15.49008</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>-70.12626</t>
+          <t>-70.13583</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>818</t>
+          <t>248</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -3849,37 +3849,37 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>464387</t>
+          <t>463689</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>BUEN PASTOR</t>
+          <t>70610</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>-15.49303</t>
+          <t>-15.48097</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>-70.1299</t>
+          <t>-70.15193</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>564</t>
+          <t>634</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -3911,32 +3911,32 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>464405</t>
+          <t>463750</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>SAGRADO CORAZON DE JESUS</t>
+          <t>70617 CESAR VALLEJO</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>-15.49045</t>
+          <t>-15.47465</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>-70.13261</t>
+          <t>-70.11238</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>680</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3973,32 +3973,32 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>464410</t>
+          <t>464698</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>ANTONIO RAYMONDI / ANTONIO RAYMONDY</t>
+          <t>TRINOMIO</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>-15.49209</t>
+          <t>-15.48886</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>-70.12534</t>
+          <t>-70.12824</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>613</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -4035,37 +4035,37 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>464467</t>
+          <t>727751</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>MARISCAL ANDRES AVELINO CACERES</t>
+          <t>SANTA MONICA</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>-15.48467</t>
+          <t>-15.49995</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>-70.15335</t>
+          <t>-70.15262</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>512</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4097,42 +4097,42 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>464580</t>
+          <t>463340</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>MARCELINO CHAMPAGNAT</t>
+          <t>70546 SEÑOR DE HUANCA</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>-15.4923</t>
+          <t>-15.50498</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>-70.13065</t>
+          <t>-70.12675</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>710</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4159,32 +4159,32 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>464698</t>
+          <t>464405</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>TRINOMIO</t>
+          <t>SAGRADO CORAZON DE JESUS</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>-15.48886</t>
+          <t>-15.49045</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>-70.12824</t>
+          <t>-70.13261</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>613</t>
+          <t>351</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -4221,37 +4221,37 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>464783</t>
+          <t>707437</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>LUZ Y CIENCIA</t>
+          <t>MARISCAL ANDRES AVELINO CACERES</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>-15.49299</t>
+          <t>-15.48477</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>-70.13381</t>
+          <t>-70.1529</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>318</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4283,37 +4283,37 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>465141</t>
+          <t>902052</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>1139 / 70538</t>
+          <t>ANGELES SCHOOL</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>-15.56746</t>
+          <t>-15.476925</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>-70.10044</t>
+          <t>-70.115798</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>290</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4345,32 +4345,32 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>511384</t>
+          <t>463321</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>SIGMA</t>
+          <t>70542</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>-15.48973</t>
+          <t>-15.489797</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>-70.12839</t>
+          <t>-70.138508</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>504</t>
+          <t>741</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -4407,32 +4407,32 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>512246</t>
+          <t>463364</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>NUEVO HORIZONTE</t>
+          <t>70548</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>-15.48828</t>
+          <t>-15.49226</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>-70.11967</t>
+          <t>-70.14352</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>651</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -4442,7 +4442,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4469,32 +4469,32 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>527196</t>
+          <t>463788</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>MARTIN LUTERO</t>
+          <t>70620</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>-15.5103</t>
+          <t>-15.47849</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>-70.11705</t>
+          <t>-70.13844</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>509</t>
+          <t>708</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -4504,7 +4504,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4531,32 +4531,32 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>527865</t>
+          <t>464274</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>ENRIQUE GUZMAN Y VALLE</t>
+          <t>PEDRO KALBERMATTER</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>-15.49327</t>
+          <t>-15.49053</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>-70.12626</t>
+          <t>-70.14365</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>333</t>
+          <t>342</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4593,32 +4593,32 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>539284</t>
+          <t>693157</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>ASOCIACION EDUCATIVA ADVENTISTA CRISTO REY</t>
+          <t>LIDER</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>-15.4899</t>
+          <t>-15.48845</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>-70.12142</t>
+          <t>-70.11766</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>535</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -4655,32 +4655,32 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>624569</t>
+          <t>511384</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>BILINGÜE PERUANO ESPAÑOL</t>
+          <t>SIGMA</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>-15.48268</t>
+          <t>-15.48973</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>-70.13806</t>
+          <t>-70.12839</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>504</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -4717,37 +4717,37 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>690314</t>
+          <t>463316</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>989</t>
+          <t>70541 VIRGEN DE FATIMA</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>-15.49285</t>
+          <t>-15.4931</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>-70.11608</t>
+          <t>-70.13178</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>830</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -4779,32 +4779,32 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>693157</t>
+          <t>463335</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>LIDER</t>
+          <t>70545 TUPAC AMARU</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>-15.48845</t>
+          <t>-15.48968</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>-70.11766</t>
+          <t>-70.127713</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>535</t>
+          <t>764</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4841,32 +4841,32 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>693162</t>
+          <t>464288</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>307 CONRADO KRETZ LENZ</t>
+          <t>AMERICANA</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>-15.48151</t>
+          <t>-15.49934</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>-70.12682</t>
+          <t>-70.13432</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>619</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -4903,37 +4903,37 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>707437</t>
+          <t>794496</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>MARISCAL ANDRES AVELINO CACERES</t>
+          <t>CLAUDIO GALENO</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>-15.48477</t>
+          <t>-15.49659</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>-70.1529</t>
+          <t>-70.13258</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>843</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -4965,42 +4965,42 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>727746</t>
+          <t>463302</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>PITAGORAS</t>
+          <t>70536</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>-15.49336</t>
+          <t>-15.487922</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>-70.1374</t>
+          <t>-70.146288</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>840</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5027,32 +5027,32 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>727751</t>
+          <t>463477</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>SANTA MONICA</t>
+          <t>70565 MARIANO NUÑEZ</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>-15.49995</t>
+          <t>-15.49028</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>-70.15262</t>
+          <t>-70.13373</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>512</t>
+          <t>914</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>37</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -5062,7 +5062,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5089,32 +5089,32 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>738759</t>
+          <t>463967</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>RODOLFO DIESEL</t>
+          <t>91 JOSE IGNACIO MIRANDA</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>-15.45792</t>
+          <t>-15.512981</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>-70.146126</t>
+          <t>-70.12539</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>503</t>
+          <t>670</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>37</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5151,37 +5151,37 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>739886</t>
+          <t>464387</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>ELENA DE SANTA MARIA</t>
+          <t>BUEN PASTOR</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>-15.52179</t>
+          <t>-15.49303</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>-70.12516</t>
+          <t>-70.1299</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>554</t>
+          <t>564</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>37</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -5213,42 +5213,42 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>742252</t>
+          <t>463359</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>1144</t>
+          <t>70547</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>-15.47207</t>
+          <t>-15.484065</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>-70.11042</t>
+          <t>-70.128818</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>865</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>38</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5275,37 +5275,37 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>743553</t>
+          <t>464306</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>LA SALLE</t>
+          <t>FRANCISCANO SAN ROMAN</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>-15.50171</t>
+          <t>-15.49307</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>-70.13281</t>
+          <t>-70.13622</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>862</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>38</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -5337,37 +5337,37 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>745316</t>
+          <t>727746</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>JOSE OLAYA BALANDRA</t>
+          <t>PITAGORAS</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>-15.436401</t>
+          <t>-15.49336</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>-70.146474</t>
+          <t>-70.1374</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>69</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -5399,32 +5399,32 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>748329</t>
+          <t>784893</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>INTERNATIONAL PERUVIAN SCHOOL</t>
+          <t>BRITANICO SCHOOL</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>-15.46999</t>
+          <t>-15.49286</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>-70.14085</t>
+          <t>-70.14694</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>47</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -5461,37 +5461,37 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>762693</t>
+          <t>463991</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>1361 SAN JACINTO</t>
+          <t>SAN FRANSISCO DE BORJA</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>-15.49313</t>
+          <t>-15.49014</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>-70.11756</t>
+          <t>-70.15721</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>735</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -5523,42 +5523,42 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>784893</t>
+          <t>463463</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>BRITANICO SCHOOL</t>
+          <t>70564</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>-15.49286</t>
+          <t>-15.48484</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>-70.14694</t>
+          <t>-70.1398</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>1002</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>41</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5585,32 +5585,32 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>794340</t>
+          <t>463953</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>ANDRES BELLO</t>
+          <t>JOSE MARIA ARGUEDAS</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>-15.48786</t>
+          <t>-15.50469</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>-70.12751</t>
+          <t>-70.13548</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>638</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>43</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -5647,32 +5647,32 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>794496</t>
+          <t>856286</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>CLAUDIO GALENO</t>
+          <t>INNOVA SCHOOLS - JULIACA</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>-15.49659</t>
+          <t>-15.51362</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>-70.13258</t>
+          <t>-70.1214</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>843</t>
+          <t>765</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>43</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -5709,32 +5709,32 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>794745</t>
+          <t>464189</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>GREGOR MENDEL</t>
+          <t>SANTA CATALINA</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>-15.496383</t>
+          <t>-15.49548</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>-70.127776</t>
+          <t>-70.13702</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>1176</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>44</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -5744,7 +5744,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5771,32 +5771,32 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>794910</t>
+          <t>464226</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>CLAUDIO GALENO</t>
+          <t>LUZ ANDINA / LUZ ANDINA REYNA DE LAS AMERICAS</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>-15.49659</t>
+          <t>-15.49249</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>-70.1326</t>
+          <t>-70.1284</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>547</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>44</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -5806,7 +5806,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5833,37 +5833,37 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>803721</t>
+          <t>464373</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>MIGUEL GRAU</t>
+          <t>FERNANDO STAHL</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>-15.50331</t>
+          <t>-15.49929</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>-70.12155</t>
+          <t>-70.12626</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>818</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>44</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -5895,32 +5895,32 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>806625</t>
+          <t>463986</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>GIORDANO LIVA</t>
+          <t>CESAR VALLEJO</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>-15.51137</t>
+          <t>-15.47556</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>-70.122643</t>
+          <t>-70.151276</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>708</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>45</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -5957,32 +5957,32 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>831074</t>
+          <t>463887</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>FE Y CIENCIA</t>
+          <t>71015 SAN JUAN BOSCO</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>-15.451127</t>
+          <t>-15.49137</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>-70.14129</t>
+          <t>-70.13106</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>1174</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>46</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -5992,7 +5992,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6019,37 +6019,37 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>837090</t>
+          <t>844199</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>THOMAS CRANMER</t>
+          <t>PACIFIC SCHOOL</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>-15.4867</t>
+          <t>-15.494</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>-70.133</t>
+          <t>-70.1364</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -6081,37 +6081,37 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>840021</t>
+          <t>855164</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>REAL AMERICAN SCHOOL</t>
+          <t>ALPHA INTERNATIONAL SCHOOL</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>-15.4828</t>
+          <t>-15.51196</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>-70.13809</t>
+          <t>-70.12626</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>335</t>
+          <t>51</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -6143,42 +6143,42 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>844199</t>
+          <t>464151</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>PACIFIC SCHOOL</t>
+          <t>JAMES BALDWIN</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>-15.494</t>
+          <t>-15.4905</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>-70.1364</t>
+          <t>-70.1299</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1008</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>51</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6205,32 +6205,32 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>844477</t>
+          <t>739886</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>GANIMEDES</t>
+          <t>ELENA DE SANTA MARIA</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>-15.46173</t>
+          <t>-15.52179</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>-70.15136</t>
+          <t>-70.12516</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>554</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>51</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -6267,32 +6267,32 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>854503</t>
+          <t>463383</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>TALENTOS LIBER</t>
+          <t>70550 LOS LIBERTADORES</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>-15.49008</t>
+          <t>-15.486474</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>-70.13583</t>
+          <t>-70.121435</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>1312</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>52</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -6302,7 +6302,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6329,37 +6329,37 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>855164</t>
+          <t>464165</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>ALPHA INTERNATIONAL SCHOOL</t>
+          <t>DANIELLE MITTERRAND</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>-15.51196</t>
+          <t>-15.49684</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>-70.12626</t>
+          <t>-70.13333</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>952</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>54</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -6391,32 +6391,32 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>855178</t>
+          <t>463892</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>THOMAS ALVA EDISON</t>
+          <t>71016 MARIA AUXILIADORA</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>-15.50134</t>
+          <t>-15.49429</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>-70.115374</t>
+          <t>-70.13477</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>277</t>
+          <t>1522</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>58</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -6426,7 +6426,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6453,32 +6453,32 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>856286</t>
+          <t>464293</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>INNOVA SCHOOLS - JULIACA</t>
+          <t>TUPAC AMARU</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>-15.51362</t>
+          <t>-15.49024</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>-70.1214</t>
+          <t>-70.12615</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>765</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>61</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6515,32 +6515,32 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>857907</t>
+          <t>463873</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>PITAGORAS</t>
+          <t>71014 MANUEL NUÑEZ BUTRON</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>-15.493121</t>
+          <t>-15.499647</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>-70.138336</t>
+          <t>-70.131946</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>1384</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>62</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -6550,7 +6550,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6577,32 +6577,32 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>858011</t>
+          <t>464325</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>SANTA ROSA DE LIMA</t>
+          <t>ADVENTISTA DEL TITICACA</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>-15.5286</t>
+          <t>-15.51645</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>-70.12222</t>
+          <t>-70.179603</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>241</t>
+          <t>1192</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>70</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>862386</t>
+          <t>463905</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>SAN IGNACIO DE RECALDE</t>
+          <t>LAS MERCEDES</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>-15.48912</t>
+          <t>-15.490577</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>-70.12647</t>
+          <t>-70.139012</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>284</t>
+          <t>1990</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>84</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -6674,7 +6674,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6701,32 +6701,32 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>900920</t>
+          <t>463934</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>SAN GINES DE ARLES</t>
+          <t>POLITECNICO REGIONAL LOS ANDES</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>-15.487268</t>
+          <t>-15.488678</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>-70.132835</t>
+          <t>-70.143998</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>2127</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>85</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -6736,7 +6736,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6763,42 +6763,42 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>902052</t>
+          <t>463948</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>ANGELES SCHOOL</t>
+          <t>32 MARIANO H. CORNEJO</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>-15.476925</t>
+          <t>-15.50433</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>-70.115798</t>
+          <t>-70.12706</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>1952</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>99</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/PUNO-SAN_ROMAN-JULIACA.xlsx
+++ b/ZonasEscolares/excels/PUNO-SAN_ROMAN-JULIACA.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>742252</t>
+          <t>902052</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1144</t>
+          <t>ANGELES SCHOOL</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-15.47207</t>
+          <t>21</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-70.11042</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-15.476925</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-70.115798</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,37 +563,37 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>762693</t>
+          <t>900920</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1361 SAN JACINTO</t>
+          <t>SAN GINES DE ARLES</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-15.49313</t>
+          <t>289</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-70.11756</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-15.487268</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-70.132835</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>464014</t>
+          <t>862386</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>SAN MARTIN</t>
+          <t>SAN IGNACIO DE RECALDE</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-15.47789</t>
+          <t>284</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-70.10889</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1534</t>
+          <t>-15.48912</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>-70.12647</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>462977</t>
+          <t>858011</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>306 BARCIA BONIFFATI</t>
+          <t>SANTA ROSA DE LIMA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-15.4889</t>
+          <t>241</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-70.13864</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>-15.5286</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-70.12222</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>624569</t>
+          <t>857907</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>BILINGÜE PERUANO ESPAÑOL</t>
+          <t>PITAGORAS</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-15.48268</t>
+          <t>233</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-70.13806</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>-15.493121</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-70.138336</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>837090</t>
+          <t>856286</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>THOMAS CRANMER</t>
+          <t>INNOVA SCHOOLS - JULIACA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-15.4867</t>
+          <t>765</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-70.133</t>
+          <t>43</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>-15.51362</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-70.1214</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>462996</t>
+          <t>855178</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>308 NIÑO JESUS DE PRAGA</t>
+          <t>THOMAS ALVA EDISON</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-15.5023</t>
+          <t>277</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-70.1267</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>245</t>
+          <t>-15.50134</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-70.115374</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,37 +935,37 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>463439</t>
+          <t>855164</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>70560 SEÑOR DE LOS MILAGROS</t>
+          <t>ALPHA INTERNATIONAL SCHOOL</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-15.49694</t>
+          <t>51</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-70.1267</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>-15.51196</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-70.12626</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>693162</t>
+          <t>854503</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>307 CONRADO KRETZ LENZ</t>
+          <t>TALENTOS LIBER</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-15.48151</t>
+          <t>248</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-70.12682</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>-15.49008</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-70.13583</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>463910</t>
+          <t>844477</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>JOSE ANTONIO ENCINAS</t>
+          <t>GANIMEDES</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-15.487692</t>
+          <t>218</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-70.124215</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2807</t>
+          <t>-15.46173</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>-70.15136</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1121,37 +1121,37 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>745316</t>
+          <t>844199</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>JOSE OLAYA BALANDRA</t>
+          <t>PACIFIC SCHOOL</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-15.436401</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-70.146474</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>-15.494</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-70.1364</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1193,22 +1193,22 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
+          <t>335</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
           <t>-15.4828</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>-70.13809</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>335</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>14</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>463707</t>
+          <t>837090</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>70612</t>
+          <t>THOMAS CRANMER</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-15.49005</t>
+          <t>253</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-70.11624</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>294</t>
+          <t>-15.4867</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-70.133</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>794910</t>
+          <t>831074</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CLAUDIO GALENO</t>
+          <t>FE Y CIENCIA</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-15.49659</t>
+          <t>202</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-70.1326</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>-15.451127</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-70.14129</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>855178</t>
+          <t>806625</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>THOMAS ALVA EDISON</t>
+          <t>GIORDANO LIVA</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-15.50134</t>
+          <t>222</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-70.115374</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>277</t>
+          <t>-15.51137</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-70.122643</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>464410</t>
+          <t>803721</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ANTONIO RAYMONDI / ANTONIO RAYMONDY</t>
+          <t>MIGUEL GRAU</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-15.49209</t>
+          <t>259</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-70.12534</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>-15.50331</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-70.12155</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>465141</t>
+          <t>794910</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1139 / 70538</t>
+          <t>CLAUDIO GALENO</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-15.56746</t>
+          <t>370</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-70.10044</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>290</t>
+          <t>-15.49659</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-70.1326</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>462963</t>
+          <t>794745</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>305</t>
+          <t>GREGOR MENDEL</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-15.49314</t>
+          <t>355</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-70.13194</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>459</t>
+          <t>-15.496383</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-70.127776</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>463024</t>
+          <t>794496</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>314</t>
+          <t>CLAUDIO GALENO</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-15.48499</t>
+          <t>843</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-70.14094</t>
+          <t>35</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>396</t>
+          <t>-15.49659</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-70.13258</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>831074</t>
+          <t>794340</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>FE Y CIENCIA</t>
+          <t>ANDRES BELLO</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-15.451127</t>
+          <t>261</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-70.14129</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>-15.48786</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-70.12751</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1741,37 +1741,37 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>857907</t>
+          <t>784893</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>PITAGORAS</t>
+          <t>BRITANICO SCHOOL</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-15.493121</t>
+          <t>47</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-70.138336</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>-15.49286</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-70.14694</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1803,37 +1803,37 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>539284</t>
+          <t>762693</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>ASOCIACION EDUCATIVA ADVENTISTA CRISTO REY</t>
+          <t>1361 SAN JACINTO</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-15.4899</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-70.12142</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>-15.49313</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-70.11756</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1875,22 +1875,22 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
+          <t>299</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
           <t>-15.46999</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>-70.14085</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>299</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>19</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1927,37 +1927,37 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>690314</t>
+          <t>745316</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>989</t>
+          <t>JOSE OLAYA BALANDRA</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-15.49285</t>
+          <t>233</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-70.11608</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>-15.436401</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>-70.146474</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>464108</t>
+          <t>743553</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>70708 COLIBRI / COLIBRI</t>
+          <t>LA SALLE</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-15.49521</t>
+          <t>243</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-70.12807</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>-15.50171</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-70.13281</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>464467</t>
+          <t>742252</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>MARISCAL ANDRES AVELINO CACERES</t>
+          <t>1144</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-15.48467</t>
+          <t>17</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-70.15335</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>-15.47207</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-70.11042</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>512246</t>
+          <t>739886</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>NUEVO HORIZONTE</t>
+          <t>ELENA DE SANTA MARIA</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-15.48828</t>
+          <t>554</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-70.11967</t>
+          <t>51</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>-15.52179</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-70.12516</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2175,32 +2175,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>794340</t>
+          <t>738759</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>ANDRES BELLO</t>
+          <t>RODOLFO DIESEL</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-15.48786</t>
+          <t>503</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-70.12751</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>-15.45792</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-70.146126</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>463444</t>
+          <t>727751</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>70561</t>
+          <t>SANTA MONICA</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-15.49782</t>
+          <t>512</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-70.12072</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>524</t>
+          <t>-15.49995</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-70.15262</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2299,37 +2299,37 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>463731</t>
+          <t>727746</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>70615</t>
+          <t>PITAGORAS</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-15.47948</t>
+          <t>69</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-70.14709</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>398</t>
+          <t>-15.49336</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-70.1374</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2361,37 +2361,37 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>463774</t>
+          <t>707437</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>70619</t>
+          <t>MARISCAL ANDRES AVELINO CACERES</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-15.48494</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-70.11835</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>493</t>
+          <t>-15.48477</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-70.1529</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2423,32 +2423,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>463825</t>
+          <t>693162</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>70663 CARLOS DANTE NAVA SILVA</t>
+          <t>307 CONRADO KRETZ LENZ</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-15.479091</t>
+          <t>299</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-70.115599</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>514</t>
+          <t>-15.48151</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-70.12682</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2485,32 +2485,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>464250</t>
+          <t>693157</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>BETHEL CHRISTIAN SCHOOL</t>
+          <t>LIDER</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-15.4884</t>
+          <t>535</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-70.12888</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>-15.48845</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-70.11766</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2547,37 +2547,37 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>464349</t>
+          <t>690314</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>BELEN</t>
+          <t>989</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-15.48461</t>
+          <t>36</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-70.1326</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>-15.49285</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-70.11608</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2609,32 +2609,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>464783</t>
+          <t>624569</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>LUZ Y CIENCIA</t>
+          <t>BILINGÜE PERUANO ESPAÑOL</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-15.49299</t>
+          <t>208</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-70.13381</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>318</t>
+          <t>-15.48268</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-70.13806</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2671,32 +2671,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>743553</t>
+          <t>539284</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>LA SALLE</t>
+          <t>ASOCIACION EDUCATIVA ADVENTISTA CRISTO REY</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-15.50171</t>
+          <t>226</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-70.13281</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>-15.4899</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-70.12142</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2733,32 +2733,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>803721</t>
+          <t>527865</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>MIGUEL GRAU</t>
+          <t>ENRIQUE GUZMAN Y VALLE</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-15.50331</t>
+          <t>333</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-70.12155</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>-15.49327</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-70.12626</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2795,32 +2795,32 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>844477</t>
+          <t>527196</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>GANIMEDES</t>
+          <t>MARTIN LUTERO</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-15.46173</t>
+          <t>509</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-70.15136</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>-15.5103</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-70.11705</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2857,32 +2857,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>463458</t>
+          <t>512246</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>70563 NUESTRA SEÑORA DEL CARMEN</t>
+          <t>NUEVO HORIZONTE</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-15.49952</t>
+          <t>326</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-70.14198</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>422</t>
+          <t>-15.48828</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-70.11967</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>858011</t>
+          <t>511384</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>SANTA ROSA DE LIMA</t>
+          <t>SIGMA</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-15.5286</t>
+          <t>504</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-70.12222</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>241</t>
+          <t>-15.48973</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-70.12839</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>463420</t>
+          <t>465141</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>70558</t>
+          <t>1139 / 70538</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-15.49349</t>
+          <t>290</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-70.12271</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>487</t>
+          <t>-15.56746</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-70.10044</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3043,32 +3043,32 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>527196</t>
+          <t>464783</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>MARTIN LUTERO</t>
+          <t>LUZ Y CIENCIA</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-15.5103</t>
+          <t>318</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-70.11705</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>509</t>
+          <t>-15.49299</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-70.13381</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3105,32 +3105,32 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>900920</t>
+          <t>464698</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>SAN GINES DE ARLES</t>
+          <t>TRINOMIO</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-15.487268</t>
+          <t>613</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>-70.132835</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>-15.48886</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-70.12824</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3167,37 +3167,37 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>806625</t>
+          <t>464580</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>GIORDANO LIVA</t>
+          <t>MARCELINO CHAMPAGNAT</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-15.51137</t>
+          <t>118</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>-70.122643</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>-15.4923</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-70.13065</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3229,37 +3229,37 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>862386</t>
+          <t>464467</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>SAN IGNACIO DE RECALDE</t>
+          <t>MARISCAL ANDRES AVELINO CACERES</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-15.48912</t>
+          <t>126</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-70.12647</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>284</t>
+          <t>-15.48467</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-70.15335</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3291,32 +3291,32 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>463378</t>
+          <t>464410</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>70549 VIRGEN DEL CARMEN</t>
+          <t>ANTONIO RAYMONDI / ANTONIO RAYMONDY</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-15.48992</t>
+          <t>285</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>-70.15561</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>523</t>
+          <t>-15.49209</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-70.12534</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3353,32 +3353,32 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>463552</t>
+          <t>464405</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>70576 MARISCAL JOSE DE SUCRE</t>
+          <t>SAGRADO CORAZON DE JESUS</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-15.48838</t>
+          <t>351</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>-70.13057</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>-15.49045</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-70.13261</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3415,32 +3415,32 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>464580</t>
+          <t>464387</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>MARCELINO CHAMPAGNAT</t>
+          <t>BUEN PASTOR</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-15.4923</t>
+          <t>564</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>-70.13065</t>
+          <t>37</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>-15.49303</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-70.1299</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3477,37 +3477,37 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>738759</t>
+          <t>464373</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>RODOLFO DIESEL</t>
+          <t>FERNANDO STAHL</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-15.45792</t>
+          <t>818</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>-70.146126</t>
+          <t>44</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>503</t>
+          <t>-15.49929</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-70.12626</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>463670</t>
+          <t>464349</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>70607 JOSE BERNARDO ALCEDO RELUERTO</t>
+          <t>BELEN</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-15.47822</t>
+          <t>259</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>-70.10937</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>543</t>
+          <t>-15.48461</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-70.1326</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3601,32 +3601,32 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>527865</t>
+          <t>464325</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>ENRIQUE GUZMAN Y VALLE</t>
+          <t>ADVENTISTA DEL TITICACA</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-15.49327</t>
+          <t>1192</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>-70.12626</t>
+          <t>70</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>333</t>
+          <t>-15.51645</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-70.179603</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3663,37 +3663,37 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>794745</t>
+          <t>464306</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>GREGOR MENDEL</t>
+          <t>FRANCISCANO SAN ROMAN</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-15.496383</t>
+          <t>862</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>-70.127776</t>
+          <t>38</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>-15.49307</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-70.13622</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -3725,32 +3725,32 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>464231</t>
+          <t>464293</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>SAN JOSE LA ESPERANZA</t>
+          <t>TUPAC AMARU</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-15.49779</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>-70.13358</t>
+          <t>61</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>-15.49024</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>-70.12615</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3760,7 +3760,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3787,32 +3787,32 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>854503</t>
+          <t>464288</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>TALENTOS LIBER</t>
+          <t>AMERICANA</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-15.49008</t>
+          <t>619</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>-70.13583</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>-15.49934</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>-70.13432</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3849,32 +3849,32 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>463689</t>
+          <t>464274</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>70610</t>
+          <t>PEDRO KALBERMATTER</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>-15.48097</t>
+          <t>342</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>-70.15193</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>634</t>
+          <t>-15.49053</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>-70.14365</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3911,32 +3911,32 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>463750</t>
+          <t>464250</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>70617 CESAR VALLEJO</t>
+          <t>BETHEL CHRISTIAN SCHOOL</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>-15.47465</t>
+          <t>272</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>-70.11238</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>-15.4884</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>-70.12888</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3973,32 +3973,32 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>464698</t>
+          <t>464231</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>TRINOMIO</t>
+          <t>SAN JOSE LA ESPERANZA</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>-15.48886</t>
+          <t>288</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>-70.12824</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>613</t>
+          <t>-15.49779</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>-70.13358</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -4035,32 +4035,32 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>727751</t>
+          <t>464226</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>SANTA MONICA</t>
+          <t>LUZ ANDINA / LUZ ANDINA REYNA DE LAS AMERICAS</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>-15.49995</t>
+          <t>547</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>-70.15262</t>
+          <t>44</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>512</t>
+          <t>-15.49249</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>-70.1284</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4097,32 +4097,32 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>463340</t>
+          <t>464189</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>70546 SEÑOR DE HUANCA</t>
+          <t>SANTA CATALINA</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>-15.50498</t>
+          <t>1176</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>-70.12675</t>
+          <t>44</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>710</t>
+          <t>-15.49548</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>-70.13702</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -4159,32 +4159,32 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>464405</t>
+          <t>464165</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>SAGRADO CORAZON DE JESUS</t>
+          <t>DANIELLE MITTERRAND</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>-15.49045</t>
+          <t>952</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>-70.13261</t>
+          <t>54</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>-15.49684</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>-70.13333</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -4221,42 +4221,42 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>707437</t>
+          <t>464151</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>MARISCAL ANDRES AVELINO CACERES</t>
+          <t>JAMES BALDWIN</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>-15.48477</t>
+          <t>1008</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>-70.1529</t>
+          <t>51</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-15.4905</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>-70.1299</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4283,42 +4283,42 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>902052</t>
+          <t>464108</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>ANGELES SCHOOL</t>
+          <t>70708 COLIBRI / COLIBRI</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>-15.476925</t>
+          <t>362</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>-70.115798</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-15.49521</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>-70.12807</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4345,32 +4345,32 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>463321</t>
+          <t>464014</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>70542</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>-15.489797</t>
+          <t>1534</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>-70.138508</t>
+          <t>105</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>-15.47789</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>-70.10889</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -4407,32 +4407,32 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>463364</t>
+          <t>463991</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>70548</t>
+          <t>SAN FRANSISCO DE BORJA</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>-15.49226</t>
+          <t>735</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>-70.14352</t>
+          <t>40</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>-15.49014</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>-70.15721</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -4442,7 +4442,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4469,32 +4469,32 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>463788</t>
+          <t>463986</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>70620</t>
+          <t>CESAR VALLEJO</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>-15.47849</t>
+          <t>708</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>-70.13844</t>
+          <t>45</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>708</t>
+          <t>-15.47556</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>-70.151276</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -4504,7 +4504,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4531,32 +4531,32 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>464274</t>
+          <t>463967</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>PEDRO KALBERMATTER</t>
+          <t>91 JOSE IGNACIO MIRANDA</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>-15.49053</t>
+          <t>670</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>-70.14365</t>
+          <t>37</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>342</t>
+          <t>-15.512981</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>-70.12539</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -4593,32 +4593,32 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>693157</t>
+          <t>463953</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>LIDER</t>
+          <t>JOSE MARIA ARGUEDAS</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>-15.48845</t>
+          <t>638</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>-70.11766</t>
+          <t>43</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>535</t>
+          <t>-15.50469</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>-70.13548</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -4655,32 +4655,32 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>511384</t>
+          <t>463948</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>SIGMA</t>
+          <t>32 MARIANO H. CORNEJO</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>-15.48973</t>
+          <t>1952</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>-70.12839</t>
+          <t>99</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>504</t>
+          <t>-15.50433</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>-70.12706</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -4690,7 +4690,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4717,32 +4717,32 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>463316</t>
+          <t>463934</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>70541 VIRGEN DE FATIMA</t>
+          <t>POLITECNICO REGIONAL LOS ANDES</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>-15.4931</t>
+          <t>2127</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>-70.13178</t>
+          <t>85</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>830</t>
+          <t>-15.488678</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>-70.143998</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4779,32 +4779,32 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>463335</t>
+          <t>463910</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>70545 TUPAC AMARU</t>
+          <t>JOSE ANTONIO ENCINAS</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>-15.48968</t>
+          <t>2807</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>-70.127713</t>
+          <t>131</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>764</t>
+          <t>-15.487692</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>-70.124215</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -4841,32 +4841,32 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>464288</t>
+          <t>463905</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>AMERICANA</t>
+          <t>LAS MERCEDES</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>-15.49934</t>
+          <t>1990</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>-70.13432</t>
+          <t>84</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>619</t>
+          <t>-15.490577</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>-70.139012</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -4876,7 +4876,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4903,32 +4903,32 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>794496</t>
+          <t>463892</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>CLAUDIO GALENO</t>
+          <t>71016 MARIA AUXILIADORA</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>-15.49659</t>
+          <t>1522</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>-70.13258</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>843</t>
+          <t>-15.49429</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>-70.13477</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4965,32 +4965,32 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>463302</t>
+          <t>463887</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>70536</t>
+          <t>71015 SAN JUAN BOSCO</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>-15.487922</t>
+          <t>1174</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>-70.146288</t>
+          <t>46</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>840</t>
+          <t>-15.49137</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>-70.13106</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -5027,32 +5027,32 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>463477</t>
+          <t>463873</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>70565 MARIANO NUÑEZ</t>
+          <t>71014 MANUEL NUÑEZ BUTRON</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>-15.49028</t>
+          <t>1384</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>-70.13373</t>
+          <t>62</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>914</t>
+          <t>-15.499647</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>-70.131946</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -5089,32 +5089,32 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>463967</t>
+          <t>463825</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>91 JOSE IGNACIO MIRANDA</t>
+          <t>70663 CARLOS DANTE NAVA SILVA</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>-15.512981</t>
+          <t>514</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>-70.12539</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>-15.479091</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>-70.115599</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5151,42 +5151,42 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>464387</t>
+          <t>463788</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>BUEN PASTOR</t>
+          <t>70620</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>-15.49303</t>
+          <t>708</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>-70.1299</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>564</t>
+          <t>-15.47849</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>-70.13844</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5213,32 +5213,32 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>463359</t>
+          <t>463774</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>70547</t>
+          <t>70619</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>-15.484065</t>
+          <t>493</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>-70.128818</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>865</t>
+          <t>-15.48494</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>-70.11835</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -5248,7 +5248,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5275,37 +5275,37 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>464306</t>
+          <t>463750</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>FRANCISCANO SAN ROMAN</t>
+          <t>70617 CESAR VALLEJO</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>-15.49307</t>
+          <t>680</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>-70.13622</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>862</t>
+          <t>-15.47465</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>-70.11238</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -5337,37 +5337,37 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>727746</t>
+          <t>463731</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>PITAGORAS</t>
+          <t>70615</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>-15.49336</t>
+          <t>398</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>-70.1374</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>-15.47948</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>-70.14709</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -5399,37 +5399,37 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>784893</t>
+          <t>463707</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>BRITANICO SCHOOL</t>
+          <t>70612</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>-15.49286</t>
+          <t>294</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>-70.14694</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>-15.49005</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>-70.11624</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -5461,32 +5461,32 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>463991</t>
+          <t>463689</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>SAN FRANSISCO DE BORJA</t>
+          <t>70610</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>-15.49014</t>
+          <t>634</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>-70.15721</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>-15.48097</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>-70.15193</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -5523,32 +5523,32 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>463463</t>
+          <t>463670</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>70564</t>
+          <t>70607 JOSE BERNARDO ALCEDO RELUERTO</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>-15.48484</t>
+          <t>543</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>-70.1398</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>1002</t>
+          <t>-15.47822</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>-70.10937</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -5558,7 +5558,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5585,32 +5585,32 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>463953</t>
+          <t>463552</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>JOSE MARIA ARGUEDAS</t>
+          <t>70576 MARISCAL JOSE DE SUCRE</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>-15.50469</t>
+          <t>521</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>-70.13548</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>-15.48838</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>-70.13057</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -5647,32 +5647,32 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>856286</t>
+          <t>463477</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>INNOVA SCHOOLS - JULIACA</t>
+          <t>70565 MARIANO NUÑEZ</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>-15.51362</t>
+          <t>914</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>-70.1214</t>
+          <t>37</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>765</t>
+          <t>-15.49028</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>-70.13373</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -5682,7 +5682,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5709,32 +5709,32 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>464189</t>
+          <t>463463</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>SANTA CATALINA</t>
+          <t>70564</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>-15.49548</t>
+          <t>1002</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>-70.13702</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>1176</t>
+          <t>-15.48484</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>-70.1398</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -5771,32 +5771,32 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>464226</t>
+          <t>463458</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>LUZ ANDINA / LUZ ANDINA REYNA DE LAS AMERICAS</t>
+          <t>70563 NUESTRA SEÑORA DEL CARMEN</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>-15.49249</t>
+          <t>422</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>-70.1284</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>547</t>
+          <t>-15.49952</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>-70.14198</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -5806,7 +5806,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5833,37 +5833,37 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>464373</t>
+          <t>463444</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>FERNANDO STAHL</t>
+          <t>70561</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>-15.49929</t>
+          <t>524</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>-70.12626</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>818</t>
+          <t>-15.49782</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>-70.12072</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -5895,32 +5895,32 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>463986</t>
+          <t>463439</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>CESAR VALLEJO</t>
+          <t>70560 SEÑOR DE LOS MILAGROS</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>-15.47556</t>
+          <t>239</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>-70.151276</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>708</t>
+          <t>-15.49694</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>-70.1267</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -5957,32 +5957,32 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>463887</t>
+          <t>463420</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>71015 SAN JUAN BOSCO</t>
+          <t>70558</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>-15.49137</t>
+          <t>487</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>-70.13106</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>1174</t>
+          <t>-15.49349</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>-70.12271</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -6019,42 +6019,42 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>844199</t>
+          <t>463383</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>PACIFIC SCHOOL</t>
+          <t>70550 LOS LIBERTADORES</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>-15.494</t>
+          <t>1312</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>-70.1364</t>
+          <t>52</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-15.486474</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>-70.121435</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6081,37 +6081,37 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>855164</t>
+          <t>463378</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>ALPHA INTERNATIONAL SCHOOL</t>
+          <t>70549 VIRGEN DEL CARMEN</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>-15.51196</t>
+          <t>523</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>-70.12626</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>-15.48992</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>-70.15561</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -6143,32 +6143,32 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>464151</t>
+          <t>463364</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>JAMES BALDWIN</t>
+          <t>70548</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>-15.4905</t>
+          <t>651</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>-70.1299</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>1008</t>
+          <t>-15.49226</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>-70.14352</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -6205,32 +6205,32 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>739886</t>
+          <t>463359</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>ELENA DE SANTA MARIA</t>
+          <t>70547</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>-15.52179</t>
+          <t>865</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>-70.12516</t>
+          <t>38</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>554</t>
+          <t>-15.484065</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>-70.128818</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -6240,7 +6240,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6267,32 +6267,32 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>463383</t>
+          <t>463340</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>70550 LOS LIBERTADORES</t>
+          <t>70546 SEÑOR DE HUANCA</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>-15.486474</t>
+          <t>710</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>-70.121435</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>1312</t>
+          <t>-15.50498</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>-70.12675</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -6329,32 +6329,32 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>464165</t>
+          <t>463335</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>DANIELLE MITTERRAND</t>
+          <t>70545 TUPAC AMARU</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>-15.49684</t>
+          <t>764</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>-70.13333</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>-15.48968</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>-70.127713</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -6364,7 +6364,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6391,32 +6391,32 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>463892</t>
+          <t>463321</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>71016 MARIA AUXILIADORA</t>
+          <t>70542</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>-15.49429</t>
+          <t>741</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>-70.13477</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>1522</t>
+          <t>-15.489797</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>-70.138508</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -6426,7 +6426,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6453,32 +6453,32 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>464293</t>
+          <t>463316</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>TUPAC AMARU</t>
+          <t>70541 VIRGEN DE FATIMA</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>-15.49024</t>
+          <t>830</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>-70.12615</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>1291</t>
+          <t>-15.4931</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>-70.13178</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6515,32 +6515,32 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>463873</t>
+          <t>463302</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>71014 MANUEL NUÑEZ BUTRON</t>
+          <t>70536</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>-15.499647</t>
+          <t>840</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>-70.131946</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>1384</t>
+          <t>-15.487922</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>-70.146288</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -6577,32 +6577,32 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>464325</t>
+          <t>463024</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>ADVENTISTA DEL TITICACA</t>
+          <t>314</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>-15.51645</t>
+          <t>396</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>-70.179603</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>1192</t>
+          <t>-15.48499</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>-70.14094</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>463905</t>
+          <t>462996</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>LAS MERCEDES</t>
+          <t>308 NIÑO JESUS DE PRAGA</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>-15.490577</t>
+          <t>245</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>-70.139012</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>1990</t>
+          <t>-15.5023</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>-70.1267</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -6674,7 +6674,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6701,32 +6701,32 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>463934</t>
+          <t>462977</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>POLITECNICO REGIONAL LOS ANDES</t>
+          <t>306 BARCIA BONIFFATI</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>-15.488678</t>
+          <t>261</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>-70.143998</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>2127</t>
+          <t>-15.4889</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>-70.13864</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -6736,7 +6736,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6763,32 +6763,32 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>463948</t>
+          <t>462963</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>32 MARIANO H. CORNEJO</t>
+          <t>305</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>-15.50433</t>
+          <t>459</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>-70.12706</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>1952</t>
+          <t>-15.49314</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>-70.13194</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -6798,7 +6798,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/PUNO-SAN_ROMAN-JULIACA.xlsx
+++ b/ZonasEscolares/excels/PUNO-SAN_ROMAN-JULIACA.xlsx
@@ -449,22 +449,22 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>alumnos</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>docentes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>longitud</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>alumnos</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>docentes</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
